--- a/Data/National Accounts/PSA-21OS_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-21OS_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9547FAE0-853C-45CC-A516-02A8059CFEF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C16C90-7298-47DC-A316-11B7E5905CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="OS" sheetId="21" r:id="rId1"/>
@@ -685,10 +685,10 @@
     <t>Table 22.7 Gross Value Added in Other Services, by Industry</t>
   </si>
   <si>
-    <t>As of January 2026</t>
+    <t>Q1 2000 to Q4 2025</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -736,10 +736,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1226,7 +1228,7 @@
     </row>
     <row r="3" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -1239,7 +1241,7 @@
     </row>
     <row r="6" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -2239,19 +2241,19 @@
         <v>64857.718869335586</v>
       </c>
       <c r="CW12" s="15">
-        <v>96262.725847254798</v>
+        <v>95779.898910273085</v>
       </c>
       <c r="CX12" s="15">
-        <v>81138.383399648039</v>
+        <v>80977.728453384785</v>
       </c>
       <c r="CY12" s="15">
-        <v>84110.070149161809</v>
+        <v>83813.301784412717</v>
       </c>
       <c r="CZ12" s="15">
-        <v>69437.591974876079</v>
+        <v>69454.61582662529</v>
       </c>
       <c r="DA12" s="15">
-        <v>106742.26753242954</v>
+        <v>107056.12581721888</v>
       </c>
       <c r="DB12" s="20"/>
       <c r="DC12" s="20"/>
@@ -2624,25 +2626,25 @@
         <v>63655.184374300108</v>
       </c>
       <c r="CU13" s="15">
-        <v>51296.819119411579</v>
+        <v>51174.055474865083</v>
       </c>
       <c r="CV13" s="15">
-        <v>42623.6871291563</v>
+        <v>43106.961901452771</v>
       </c>
       <c r="CW13" s="15">
-        <v>59898.361376499568</v>
+        <v>59506.827764520633</v>
       </c>
       <c r="CX13" s="15">
-        <v>69131.144472028624</v>
+        <v>68785.358065558001</v>
       </c>
       <c r="CY13" s="15">
-        <v>55752.55048933316</v>
+        <v>55215.149486648275</v>
       </c>
       <c r="CZ13" s="15">
-        <v>45065.717033920373</v>
+        <v>45663.156258736199</v>
       </c>
       <c r="DA13" s="15">
-        <v>63967.046305951779</v>
+        <v>63426.923117927676</v>
       </c>
       <c r="DB13" s="20"/>
       <c r="DC13" s="20"/>
@@ -3195,25 +3197,25 @@
         <v>136405.28269873373</v>
       </c>
       <c r="CU15" s="16">
-        <v>127420.71174577823</v>
+        <v>127297.94810123174</v>
       </c>
       <c r="CV15" s="16">
-        <v>107481.40599849189</v>
+        <v>107964.68077078836</v>
       </c>
       <c r="CW15" s="16">
-        <v>156161.08722375438</v>
+        <v>155286.72667479372</v>
       </c>
       <c r="CX15" s="16">
-        <v>150269.52787167666</v>
+        <v>149763.08651894279</v>
       </c>
       <c r="CY15" s="16">
-        <v>139862.62063849496</v>
+        <v>139028.451271061</v>
       </c>
       <c r="CZ15" s="16">
-        <v>114503.30900879645</v>
+        <v>115117.77208536149</v>
       </c>
       <c r="DA15" s="16">
-        <v>170709.31383838132</v>
+        <v>170483.04893514657</v>
       </c>
       <c r="DB15" s="20"/>
       <c r="DC15" s="20"/>
@@ -4086,7 +4088,7 @@
     </row>
     <row r="22" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -4411,7 +4413,7 @@
     </row>
     <row r="25" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -5619,19 +5621,19 @@
         <v>56399.549041322942</v>
       </c>
       <c r="CW31" s="15">
-        <v>83183.348883602303</v>
+        <v>82766.124447083857</v>
       </c>
       <c r="CX31" s="15">
-        <v>70517.226555602247</v>
+        <v>70377.601623871451</v>
       </c>
       <c r="CY31" s="15">
-        <v>72620.872656628926</v>
+        <v>72365.466107183049</v>
       </c>
       <c r="CZ31" s="15">
-        <v>59318.562641229524</v>
+        <v>59333.054933798529</v>
       </c>
       <c r="DA31" s="15">
-        <v>90436.337810524565</v>
+        <v>90702.251159791005</v>
       </c>
       <c r="DB31" s="20"/>
       <c r="DC31" s="20"/>
@@ -6004,25 +6006,25 @@
         <v>51050.658714114266</v>
       </c>
       <c r="CU32" s="15">
-        <v>42087.733529115139</v>
+        <v>41987.009085622689</v>
       </c>
       <c r="CV32" s="15">
-        <v>35007.935767934476</v>
+        <v>35404.861827746063</v>
       </c>
       <c r="CW32" s="15">
-        <v>47700.819859676805</v>
+        <v>47389.017101390607</v>
       </c>
       <c r="CX32" s="15">
-        <v>53701.582169576934</v>
+        <v>53434.001561037046</v>
       </c>
       <c r="CY32" s="15">
-        <v>44550.489569939091</v>
+        <v>44356.187331691741</v>
       </c>
       <c r="CZ32" s="15">
-        <v>36065.79275061316</v>
+        <v>36544.03636122941</v>
       </c>
       <c r="DA32" s="15">
-        <v>49742.628356635018</v>
+        <v>49322.966747712213</v>
       </c>
       <c r="DB32" s="20"/>
       <c r="DC32" s="20"/>
@@ -6575,25 +6577,25 @@
         <v>115837.97533440292</v>
       </c>
       <c r="CU34" s="16">
-        <v>109046.7386534962</v>
+        <v>108946.01421000375</v>
       </c>
       <c r="CV34" s="16">
-        <v>91407.48480925741</v>
+        <v>91804.410869069005</v>
       </c>
       <c r="CW34" s="16">
-        <v>130884.16874327911</v>
+        <v>130155.14154847446</v>
       </c>
       <c r="CX34" s="16">
-        <v>124218.80872517917</v>
+        <v>123811.6031849085</v>
       </c>
       <c r="CY34" s="16">
-        <v>117171.36222656802</v>
+        <v>116721.65343887478</v>
       </c>
       <c r="CZ34" s="16">
-        <v>95384.355391842691</v>
+        <v>95877.091295027931</v>
       </c>
       <c r="DA34" s="16">
-        <v>140178.96616715958</v>
+        <v>140025.21790750322</v>
       </c>
       <c r="DB34" s="20"/>
       <c r="DC34" s="20"/>
@@ -7466,7 +7468,7 @@
     </row>
     <row r="41" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -7791,7 +7793,7 @@
     </row>
     <row r="44" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -8956,19 +8958,19 @@
         <v>10.131293453703492</v>
       </c>
       <c r="CS50" s="12">
-        <v>14.593782876482805</v>
+        <v>14.019012479151741</v>
       </c>
       <c r="CT50" s="12">
-        <v>11.530273179572006</v>
+        <v>11.309441936778626</v>
       </c>
       <c r="CU50" s="12">
-        <v>10.491026203813746</v>
+        <v>10.101177032272162</v>
       </c>
       <c r="CV50" s="12">
-        <v>7.0614156423960139</v>
+        <v>7.0876636388503869</v>
       </c>
       <c r="CW50" s="12">
-        <v>10.886396154834841</v>
+        <v>11.773062025790409</v>
       </c>
       <c r="CX50" s="14"/>
       <c r="CY50" s="14"/>
@@ -9329,25 +9331,25 @@
         <v>18.839645842897681</v>
       </c>
       <c r="CQ51" s="12">
-        <v>15.858785925278383</v>
+        <v>15.581512459650625</v>
       </c>
       <c r="CR51" s="12">
-        <v>9.3631718361577612</v>
+        <v>10.603150484804161</v>
       </c>
       <c r="CS51" s="12">
-        <v>14.017243519027801</v>
+        <v>13.271954630367119</v>
       </c>
       <c r="CT51" s="12">
-        <v>8.6025359152668699</v>
+        <v>8.0593179356638984</v>
       </c>
       <c r="CU51" s="12">
-        <v>8.6861747890240224</v>
+        <v>7.8967632607660647</v>
       </c>
       <c r="CV51" s="12">
-        <v>5.7292788804599297</v>
+        <v>5.9298875275115961</v>
       </c>
       <c r="CW51" s="12">
-        <v>6.7926481392001961</v>
+        <v>6.5876396048526971</v>
       </c>
       <c r="CX51" s="14"/>
       <c r="CY51" s="14"/>
@@ -9885,25 +9887,25 @@
         <v>14.325527067753143</v>
       </c>
       <c r="CQ53" s="12">
-        <v>15.015834252451128</v>
+        <v>14.905022102684157</v>
       </c>
       <c r="CR53" s="12">
-        <v>9.825393553786995</v>
+        <v>10.319207730937066</v>
       </c>
       <c r="CS53" s="12">
-        <v>14.371952979659426</v>
+        <v>13.731573706110268</v>
       </c>
       <c r="CT53" s="12">
-        <v>10.164008972851633</v>
+        <v>9.7927320378868643</v>
       </c>
       <c r="CU53" s="12">
-        <v>9.7644321101737717</v>
+        <v>9.214997841521182</v>
       </c>
       <c r="CV53" s="12">
-        <v>6.5331328196461129</v>
+        <v>6.6253994023835645</v>
       </c>
       <c r="CW53" s="12">
-        <v>9.3161663211153325</v>
+        <v>9.7859762941474315</v>
       </c>
       <c r="CX53" s="14"/>
       <c r="CY53" s="14"/>
@@ -10768,7 +10770,7 @@
     </row>
     <row r="60" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -11093,7 +11095,7 @@
     </row>
     <row r="63" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -12279,19 +12281,19 @@
         <v>6.5347817839216447</v>
       </c>
       <c r="CS69" s="12">
-        <v>11.642604948762482</v>
+        <v>11.082636835355814</v>
       </c>
       <c r="CT69" s="12">
-        <v>8.844184686481114</v>
+        <v>8.6286719302588892</v>
       </c>
       <c r="CU69" s="12">
-        <v>8.4557223061043914</v>
+        <v>8.0742851133452689</v>
       </c>
       <c r="CV69" s="12">
-        <v>5.1755974108372129</v>
+        <v>5.2012931704937131</v>
       </c>
       <c r="CW69" s="12">
-        <v>8.7192797888809395</v>
+        <v>9.5886170407569011</v>
       </c>
       <c r="CX69" s="14"/>
       <c r="CY69" s="14"/>
@@ -12652,25 +12654,25 @@
         <v>13.017499611746956</v>
       </c>
       <c r="CQ70" s="12">
-        <v>11.314317026440193</v>
+        <v>11.047919392377167</v>
       </c>
       <c r="CR70" s="12">
-        <v>5.2478118161361351</v>
+        <v>6.441129797661759</v>
       </c>
       <c r="CS70" s="12">
-        <v>9.7548708073445169</v>
+        <v>9.0374434852618606</v>
       </c>
       <c r="CT70" s="12">
-        <v>5.1927311463461052</v>
+        <v>4.6685839261538149</v>
       </c>
       <c r="CU70" s="12">
-        <v>5.8514817366449137</v>
+        <v>5.6426458984912813</v>
       </c>
       <c r="CV70" s="12">
-        <v>3.0217633787126204</v>
+        <v>3.2175652570704187</v>
       </c>
       <c r="CW70" s="12">
-        <v>4.2804473863649974</v>
+        <v>4.081008142000158</v>
       </c>
       <c r="CX70" s="14"/>
       <c r="CY70" s="14"/>
@@ -13207,25 +13209,25 @@
         <v>9.0193737408293231</v>
       </c>
       <c r="CQ72" s="12">
-        <v>10.545848761978235</v>
+        <v>10.443739618372078</v>
       </c>
       <c r="CR72" s="12">
-        <v>6.0381867474228272</v>
+        <v>6.4986448788663154</v>
       </c>
       <c r="CS72" s="12">
-        <v>10.947145383693368</v>
+        <v>10.329167770760634</v>
       </c>
       <c r="CT72" s="12">
-        <v>7.2349619082881418</v>
+        <v>6.8834316444906563</v>
       </c>
       <c r="CU72" s="12">
-        <v>7.4505883196455756</v>
+        <v>7.1371488762156616</v>
       </c>
       <c r="CV72" s="12">
-        <v>4.3507056242537772</v>
+        <v>4.4362578958949683</v>
       </c>
       <c r="CW72" s="12">
-        <v>7.1015444519586026</v>
+        <v>7.5833165264184146</v>
       </c>
       <c r="CX72" s="14"/>
       <c r="CY72" s="14"/>
@@ -13985,7 +13987,7 @@
     </row>
     <row r="78" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -14310,7 +14312,7 @@
     </row>
     <row r="81" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -15518,19 +15520,19 @@
         <v>114.99687492503796</v>
       </c>
       <c r="CW87" s="12">
-        <v>115.72355181558554</v>
+        <v>115.72355181558551</v>
       </c>
       <c r="CX87" s="12">
-        <v>115.06179037780377</v>
+        <v>115.06179037780375</v>
       </c>
       <c r="CY87" s="12">
-        <v>115.82079238686225</v>
+        <v>115.81947342158188</v>
       </c>
       <c r="CZ87" s="12">
-        <v>117.05879050854359</v>
+        <v>117.05889053600897</v>
       </c>
       <c r="DA87" s="12">
-        <v>118.03028529977402</v>
+        <v>118.03028529977399</v>
       </c>
       <c r="DB87" s="20"/>
       <c r="DC87" s="20"/>
@@ -15903,25 +15905,25 @@
         <v>124.69023118932057</v>
       </c>
       <c r="CU88" s="12">
-        <v>121.88068783491477</v>
+        <v>121.88068783491475</v>
       </c>
       <c r="CV88" s="12">
-        <v>121.75435710264719</v>
+        <v>121.75435710264722</v>
       </c>
       <c r="CW88" s="12">
-        <v>125.57092635452535</v>
+        <v>125.57092635452538</v>
       </c>
       <c r="CX88" s="12">
-        <v>128.73204415789607</v>
+        <v>128.72956555010256</v>
       </c>
       <c r="CY88" s="12">
-        <v>125.14464156854692</v>
+        <v>124.48127940698363</v>
       </c>
       <c r="CZ88" s="12">
-        <v>124.95418399794971</v>
+        <v>124.95378399738438</v>
       </c>
       <c r="DA88" s="12">
-        <v>128.59603205390212</v>
+        <v>128.59510954066781</v>
       </c>
       <c r="DB88" s="20"/>
       <c r="DC88" s="20"/>
@@ -16474,25 +16476,25 @@
         <v>117.75523726563486</v>
       </c>
       <c r="CU90" s="12">
-        <v>116.8496310106684</v>
+        <v>116.84497962068892</v>
       </c>
       <c r="CV90" s="12">
-        <v>117.58490699396924</v>
+        <v>117.6029340515752</v>
       </c>
       <c r="CW90" s="12">
-        <v>119.31243382845966</v>
+        <v>119.30894533041506</v>
       </c>
       <c r="CX90" s="12">
-        <v>120.97163820346395</v>
+        <v>120.96046143209745</v>
       </c>
       <c r="CY90" s="12">
-        <v>119.36587403332399</v>
+        <v>119.11110507346258</v>
       </c>
       <c r="CZ90" s="12">
-        <v>120.04411891070852</v>
+        <v>120.0680689520786</v>
       </c>
       <c r="DA90" s="12">
-        <v>121.77954974701063</v>
+        <v>121.75167550730966</v>
       </c>
       <c r="DB90" s="20"/>
       <c r="DC90" s="20"/>
@@ -17217,7 +17219,7 @@
     </row>
     <row r="97" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -17542,7 +17544,7 @@
     </row>
     <row r="100" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -18744,25 +18746,25 @@
         <v>53.333783622669742</v>
       </c>
       <c r="CU106" s="12">
-        <v>59.742165605105271</v>
+        <v>59.799779777935058</v>
       </c>
       <c r="CV106" s="12">
-        <v>60.343199148553786</v>
+        <v>60.073089093858478</v>
       </c>
       <c r="CW106" s="12">
-        <v>61.643222110336225</v>
+        <v>61.679385586418036</v>
       </c>
       <c r="CX106" s="12">
-        <v>53.995234129527923</v>
+        <v>54.070552587831656</v>
       </c>
       <c r="CY106" s="12">
-        <v>60.137633461453852</v>
+        <v>60.284999953717097</v>
       </c>
       <c r="CZ106" s="12">
-        <v>60.642432586416952</v>
+        <v>60.333530234691899</v>
       </c>
       <c r="DA106" s="12">
-        <v>62.528672356733594</v>
+        <v>62.795759746145841</v>
       </c>
       <c r="DB106" s="20"/>
       <c r="DC106" s="20"/>
@@ -19135,25 +19137,25 @@
         <v>46.666216377330251</v>
       </c>
       <c r="CU107" s="12">
-        <v>40.257834394894729</v>
+        <v>40.200220222064928</v>
       </c>
       <c r="CV107" s="12">
-        <v>39.656800851446221</v>
+        <v>39.926910906141515</v>
       </c>
       <c r="CW107" s="12">
-        <v>38.356777889663768</v>
+        <v>38.320614413581964</v>
       </c>
       <c r="CX107" s="12">
-        <v>46.00476587047207</v>
+        <v>45.929447412168336</v>
       </c>
       <c r="CY107" s="12">
-        <v>39.862366538546148</v>
+        <v>39.715000046282903</v>
       </c>
       <c r="CZ107" s="12">
-        <v>39.357567413583041</v>
+        <v>39.666469765308101</v>
       </c>
       <c r="DA107" s="12">
-        <v>37.471327643266406</v>
+        <v>37.204240253854152</v>
       </c>
       <c r="DB107" s="20"/>
       <c r="DC107" s="20"/>
@@ -20597,7 +20599,7 @@
     </row>
     <row r="116" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -20922,7 +20924,7 @@
     </row>
     <row r="119" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -22124,25 +22126,25 @@
         <v>55.929255007487477</v>
       </c>
       <c r="CU125" s="12">
-        <v>61.403950224635409</v>
+        <v>61.460720348439033</v>
       </c>
       <c r="CV125" s="12">
-        <v>61.701237222546354</v>
+        <v>61.434465411209594</v>
       </c>
       <c r="CW125" s="12">
-        <v>63.554935392347645</v>
+        <v>63.590361058659198</v>
       </c>
       <c r="CX125" s="12">
-        <v>56.768558062421981</v>
+        <v>56.842492798324287</v>
       </c>
       <c r="CY125" s="12">
-        <v>61.978346309745739</v>
+        <v>61.998321626826211</v>
       </c>
       <c r="CZ125" s="12">
-        <v>62.188985182681719</v>
+        <v>61.884496215286703</v>
       </c>
       <c r="DA125" s="12">
-        <v>64.514912817006874</v>
+        <v>64.775654353708205</v>
       </c>
       <c r="DB125" s="20"/>
       <c r="DC125" s="20"/>
@@ -22515,25 +22517,25 @@
         <v>44.070744992512523</v>
       </c>
       <c r="CU126" s="12">
-        <v>38.596049775364598</v>
+        <v>38.539279651560967</v>
       </c>
       <c r="CV126" s="12">
-        <v>38.298762777453646</v>
+        <v>38.565534588790399</v>
       </c>
       <c r="CW126" s="12">
-        <v>36.445064607652363</v>
+        <v>36.409638941340802</v>
       </c>
       <c r="CX126" s="12">
-        <v>43.231441937578019</v>
+        <v>43.157507201675713</v>
       </c>
       <c r="CY126" s="12">
-        <v>38.021653690254261</v>
+        <v>38.001678373173789</v>
       </c>
       <c r="CZ126" s="12">
-        <v>37.811014817318274</v>
+        <v>38.115503784713312</v>
       </c>
       <c r="DA126" s="12">
-        <v>35.485087182993134</v>
+        <v>35.224345646291802</v>
       </c>
       <c r="DB126" s="20"/>
       <c r="DC126" s="20"/>

--- a/Data/National Accounts/PSA-21OS_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-21OS_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C16C90-7298-47DC-A316-11B7E5905CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FF9D2FF-874D-4C6B-BDC3-232DD561DEEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="OS" sheetId="21" r:id="rId1"/>
@@ -356,7 +356,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">OS!$A$1:$DA$131</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">OS!$A$1:$DB$131</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -530,7 +530,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="54">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -685,10 +685,13 @@
     <t>Table 22.7 Gross Value Added in Other Services, by Industry</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>As of May 2026</t>
   </si>
   <si>
-    <t>As of April 2026</t>
+    <t>Q1 2000 to Q1 2026</t>
+  </si>
+  <si>
+    <t>2025 - 2026</t>
   </si>
 </sst>
 </file>
@@ -1212,8 +1215,8 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.85546875" style="3" customWidth="1"/>
-    <col min="2" max="105" width="13" style="21" customWidth="1"/>
-    <col min="106" max="16384" width="10" style="21"/>
+    <col min="2" max="106" width="13" style="21" customWidth="1"/>
+    <col min="107" max="16384" width="10" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -1228,7 +1231,7 @@
     </row>
     <row r="3" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -1241,7 +1244,7 @@
     </row>
     <row r="6" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -1355,6 +1358,7 @@
       <c r="CY8" s="3"/>
       <c r="CZ8" s="3"/>
       <c r="DA8" s="3"/>
+      <c r="DB8" s="3"/>
     </row>
     <row r="9" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="13"/>
@@ -1514,6 +1518,9 @@
       <c r="CY9" s="25"/>
       <c r="CZ9" s="25"/>
       <c r="DA9" s="25"/>
+      <c r="DB9" s="25">
+        <v>2026</v>
+      </c>
     </row>
     <row r="10" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
@@ -1830,6 +1837,9 @@
       </c>
       <c r="DA10" s="11" t="s">
         <v>5</v>
+      </c>
+      <c r="DB10" s="11" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:179" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1938,6 +1948,7 @@
       <c r="CY11" s="3"/>
       <c r="CZ11" s="3"/>
       <c r="DA11" s="3"/>
+      <c r="DB11" s="3"/>
     </row>
     <row r="12" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="24" t="s">
@@ -2255,7 +2266,9 @@
       <c r="DA12" s="15">
         <v>107056.12581721888</v>
       </c>
-      <c r="DB12" s="20"/>
+      <c r="DB12" s="15">
+        <v>87385.601711987081</v>
+      </c>
       <c r="DC12" s="20"/>
       <c r="DD12" s="20"/>
       <c r="DE12" s="20"/>
@@ -2646,7 +2659,9 @@
       <c r="DA13" s="15">
         <v>63426.923117927676</v>
       </c>
-      <c r="DB13" s="20"/>
+      <c r="DB13" s="15">
+        <v>73627.129544531592</v>
+      </c>
       <c r="DC13" s="20"/>
       <c r="DD13" s="20"/>
       <c r="DE13" s="20"/>
@@ -2826,7 +2841,7 @@
       <c r="CY14" s="16"/>
       <c r="CZ14" s="16"/>
       <c r="DA14" s="16"/>
-      <c r="DB14" s="20"/>
+      <c r="DB14" s="16"/>
       <c r="DC14" s="20"/>
       <c r="DD14" s="20"/>
       <c r="DE14" s="20"/>
@@ -3217,7 +3232,9 @@
       <c r="DA15" s="16">
         <v>170483.04893514657</v>
       </c>
-      <c r="DB15" s="20"/>
+      <c r="DB15" s="16">
+        <v>161012.73125651869</v>
+      </c>
       <c r="DC15" s="20"/>
       <c r="DD15" s="20"/>
       <c r="DE15" s="20"/>
@@ -3398,6 +3415,7 @@
       <c r="CY16" s="9"/>
       <c r="CZ16" s="9"/>
       <c r="DA16" s="9"/>
+      <c r="DB16" s="9"/>
     </row>
     <row r="17" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
@@ -3507,6 +3525,7 @@
       <c r="CY17" s="3"/>
       <c r="CZ17" s="3"/>
       <c r="DA17" s="3"/>
+      <c r="DB17" s="3"/>
     </row>
     <row r="18" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="7"/>
@@ -3613,7 +3632,7 @@
       <c r="CY18" s="7"/>
       <c r="CZ18" s="7"/>
       <c r="DA18" s="7"/>
-      <c r="DB18" s="20"/>
+      <c r="DB18" s="7"/>
       <c r="DC18" s="20"/>
       <c r="DD18" s="20"/>
       <c r="DE18" s="20"/>
@@ -3793,7 +3812,7 @@
       <c r="CY19" s="7"/>
       <c r="CZ19" s="7"/>
       <c r="DA19" s="7"/>
-      <c r="DB19" s="20"/>
+      <c r="DB19" s="7"/>
       <c r="DC19" s="20"/>
       <c r="DD19" s="20"/>
       <c r="DE19" s="20"/>
@@ -3976,6 +3995,7 @@
       <c r="CY20" s="3"/>
       <c r="CZ20" s="3"/>
       <c r="DA20" s="3"/>
+      <c r="DB20" s="3"/>
     </row>
     <row r="21" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
@@ -4085,10 +4105,11 @@
       <c r="CY21" s="3"/>
       <c r="CZ21" s="3"/>
       <c r="DA21" s="3"/>
+      <c r="DB21" s="3"/>
     </row>
     <row r="22" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -4194,6 +4215,7 @@
       <c r="CY22" s="3"/>
       <c r="CZ22" s="3"/>
       <c r="DA22" s="3"/>
+      <c r="DB22" s="3"/>
     </row>
     <row r="23" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="3"/>
@@ -4301,6 +4323,7 @@
       <c r="CY23" s="3"/>
       <c r="CZ23" s="3"/>
       <c r="DA23" s="3"/>
+      <c r="DB23" s="3"/>
     </row>
     <row r="24" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
@@ -4410,10 +4433,11 @@
       <c r="CY24" s="3"/>
       <c r="CZ24" s="3"/>
       <c r="DA24" s="3"/>
+      <c r="DB24" s="3"/>
     </row>
     <row r="25" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -4519,6 +4543,7 @@
       <c r="CY25" s="3"/>
       <c r="CZ25" s="3"/>
       <c r="DA25" s="3"/>
+      <c r="DB25" s="3"/>
     </row>
     <row r="26" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
@@ -4628,6 +4653,7 @@
       <c r="CY26" s="3"/>
       <c r="CZ26" s="3"/>
       <c r="DA26" s="3"/>
+      <c r="DB26" s="3"/>
     </row>
     <row r="27" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="3"/>
@@ -4735,6 +4761,7 @@
       <c r="CY27" s="3"/>
       <c r="CZ27" s="3"/>
       <c r="DA27" s="3"/>
+      <c r="DB27" s="3"/>
     </row>
     <row r="28" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A28" s="13"/>
@@ -4894,6 +4921,9 @@
       <c r="CY28" s="25"/>
       <c r="CZ28" s="25"/>
       <c r="DA28" s="25"/>
+      <c r="DB28" s="25">
+        <v>2026</v>
+      </c>
     </row>
     <row r="29" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
@@ -5210,6 +5240,9 @@
       </c>
       <c r="DA29" s="11" t="s">
         <v>5</v>
+      </c>
+      <c r="DB29" s="11" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:179" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -5318,6 +5351,7 @@
       <c r="CY30" s="3"/>
       <c r="CZ30" s="3"/>
       <c r="DA30" s="3"/>
+      <c r="DB30" s="3"/>
     </row>
     <row r="31" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="24" t="s">
@@ -5635,7 +5669,9 @@
       <c r="DA31" s="15">
         <v>90702.251159791005</v>
       </c>
-      <c r="DB31" s="20"/>
+      <c r="DB31" s="15">
+        <v>73146.891247984342</v>
+      </c>
       <c r="DC31" s="20"/>
       <c r="DD31" s="20"/>
       <c r="DE31" s="20"/>
@@ -6026,7 +6062,9 @@
       <c r="DA32" s="15">
         <v>49322.966747712213</v>
       </c>
-      <c r="DB32" s="20"/>
+      <c r="DB32" s="15">
+        <v>55509.473152690858</v>
+      </c>
       <c r="DC32" s="20"/>
       <c r="DD32" s="20"/>
       <c r="DE32" s="20"/>
@@ -6206,7 +6244,7 @@
       <c r="CY33" s="16"/>
       <c r="CZ33" s="16"/>
       <c r="DA33" s="16"/>
-      <c r="DB33" s="20"/>
+      <c r="DB33" s="16"/>
       <c r="DC33" s="20"/>
       <c r="DD33" s="20"/>
       <c r="DE33" s="20"/>
@@ -6597,7 +6635,9 @@
       <c r="DA34" s="16">
         <v>140025.21790750322</v>
       </c>
-      <c r="DB34" s="20"/>
+      <c r="DB34" s="16">
+        <v>128656.3644006752</v>
+      </c>
       <c r="DC34" s="20"/>
       <c r="DD34" s="20"/>
       <c r="DE34" s="20"/>
@@ -6778,6 +6818,7 @@
       <c r="CY35" s="9"/>
       <c r="CZ35" s="9"/>
       <c r="DA35" s="9"/>
+      <c r="DB35" s="9"/>
     </row>
     <row r="36" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="10" t="s">
@@ -6887,6 +6928,7 @@
       <c r="CY36" s="3"/>
       <c r="CZ36" s="3"/>
       <c r="DA36" s="3"/>
+      <c r="DB36" s="3"/>
     </row>
     <row r="37" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="7"/>
@@ -6993,7 +7035,7 @@
       <c r="CY37" s="6"/>
       <c r="CZ37" s="6"/>
       <c r="DA37" s="6"/>
-      <c r="DB37" s="20"/>
+      <c r="DB37" s="6"/>
       <c r="DC37" s="20"/>
       <c r="DD37" s="20"/>
       <c r="DE37" s="20"/>
@@ -7173,7 +7215,7 @@
       <c r="CY38" s="6"/>
       <c r="CZ38" s="6"/>
       <c r="DA38" s="6"/>
-      <c r="DB38" s="20"/>
+      <c r="DB38" s="6"/>
       <c r="DC38" s="20"/>
       <c r="DD38" s="20"/>
       <c r="DE38" s="20"/>
@@ -7356,6 +7398,7 @@
       <c r="CY39" s="26"/>
       <c r="CZ39" s="26"/>
       <c r="DA39" s="26"/>
+      <c r="DB39" s="26"/>
     </row>
     <row r="40" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
@@ -7465,10 +7508,11 @@
       <c r="CY40" s="26"/>
       <c r="CZ40" s="26"/>
       <c r="DA40" s="26"/>
+      <c r="DB40" s="26"/>
     </row>
     <row r="41" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -7574,6 +7618,7 @@
       <c r="CY41" s="26"/>
       <c r="CZ41" s="26"/>
       <c r="DA41" s="26"/>
+      <c r="DB41" s="26"/>
     </row>
     <row r="42" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="3"/>
@@ -7681,6 +7726,7 @@
       <c r="CY42" s="26"/>
       <c r="CZ42" s="26"/>
       <c r="DA42" s="26"/>
+      <c r="DB42" s="26"/>
     </row>
     <row r="43" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
@@ -7790,10 +7836,11 @@
       <c r="CY43" s="26"/>
       <c r="CZ43" s="26"/>
       <c r="DA43" s="26"/>
+      <c r="DB43" s="26"/>
     </row>
     <row r="44" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -7899,6 +7946,7 @@
       <c r="CY44" s="26"/>
       <c r="CZ44" s="26"/>
       <c r="DA44" s="26"/>
+      <c r="DB44" s="26"/>
     </row>
     <row r="45" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
@@ -7987,6 +8035,7 @@
       <c r="CY45" s="18"/>
       <c r="CZ45" s="18"/>
       <c r="DA45" s="18"/>
+      <c r="DB45" s="18"/>
     </row>
     <row r="46" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="3"/>
@@ -8094,6 +8143,7 @@
       <c r="CY46" s="26"/>
       <c r="CZ46" s="26"/>
       <c r="DA46" s="26"/>
+      <c r="DB46" s="26"/>
     </row>
     <row r="47" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A47" s="13"/>
@@ -8247,10 +8297,13 @@
       <c r="CU47" s="25"/>
       <c r="CV47" s="25"/>
       <c r="CW47" s="25"/>
-      <c r="CX47" s="27"/>
+      <c r="CX47" s="25" t="s">
+        <v>53</v>
+      </c>
       <c r="CY47" s="27"/>
       <c r="CZ47" s="27"/>
       <c r="DA47" s="27"/>
+      <c r="DB47" s="27"/>
     </row>
     <row r="48" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
@@ -8556,10 +8609,13 @@
       <c r="CW48" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="CX48" s="28"/>
+      <c r="CX48" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="CY48" s="28"/>
       <c r="CZ48" s="28"/>
       <c r="DA48" s="28"/>
+      <c r="DB48" s="28"/>
     </row>
     <row r="49" spans="1:175" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="5"/>
@@ -8663,10 +8719,11 @@
       <c r="CU49" s="3"/>
       <c r="CV49" s="3"/>
       <c r="CW49" s="3"/>
-      <c r="CX49" s="26"/>
+      <c r="CX49" s="3"/>
       <c r="CY49" s="26"/>
       <c r="CZ49" s="26"/>
       <c r="DA49" s="26"/>
+      <c r="DB49" s="26"/>
     </row>
     <row r="50" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="24" t="s">
@@ -8972,11 +9029,13 @@
       <c r="CW50" s="12">
         <v>11.773062025790409</v>
       </c>
-      <c r="CX50" s="14"/>
+      <c r="CX50" s="12">
+        <v>7.9131304137421097</v>
+      </c>
       <c r="CY50" s="14"/>
       <c r="CZ50" s="14"/>
       <c r="DA50" s="14"/>
-      <c r="DB50" s="20"/>
+      <c r="DB50" s="14"/>
       <c r="DC50" s="20"/>
       <c r="DD50" s="20"/>
       <c r="DE50" s="20"/>
@@ -9351,11 +9410,13 @@
       <c r="CW51" s="12">
         <v>6.5876396048526971</v>
       </c>
-      <c r="CX51" s="14"/>
+      <c r="CX51" s="12">
+        <v>7.0389565674121997</v>
+      </c>
       <c r="CY51" s="14"/>
       <c r="CZ51" s="14"/>
       <c r="DA51" s="14"/>
-      <c r="DB51" s="20"/>
+      <c r="DB51" s="14"/>
       <c r="DC51" s="20"/>
       <c r="DD51" s="20"/>
       <c r="DE51" s="20"/>
@@ -9528,11 +9589,11 @@
       <c r="CU52" s="7"/>
       <c r="CV52" s="7"/>
       <c r="CW52" s="7"/>
-      <c r="CX52" s="6"/>
+      <c r="CX52" s="7"/>
       <c r="CY52" s="6"/>
       <c r="CZ52" s="6"/>
       <c r="DA52" s="6"/>
-      <c r="DB52" s="20"/>
+      <c r="DB52" s="6"/>
       <c r="DC52" s="20"/>
       <c r="DD52" s="20"/>
       <c r="DE52" s="20"/>
@@ -9907,11 +9968,13 @@
       <c r="CW53" s="12">
         <v>9.7859762941474315</v>
       </c>
-      <c r="CX53" s="14"/>
+      <c r="CX53" s="12">
+        <v>7.5116271967010846</v>
+      </c>
       <c r="CY53" s="14"/>
       <c r="CZ53" s="14"/>
       <c r="DA53" s="14"/>
-      <c r="DB53" s="20"/>
+      <c r="DB53" s="14"/>
       <c r="DC53" s="20"/>
       <c r="DD53" s="20"/>
       <c r="DE53" s="20"/>
@@ -10084,10 +10147,11 @@
       <c r="CU54" s="9"/>
       <c r="CV54" s="9"/>
       <c r="CW54" s="9"/>
-      <c r="CX54" s="29"/>
+      <c r="CX54" s="9"/>
       <c r="CY54" s="29"/>
       <c r="CZ54" s="29"/>
       <c r="DA54" s="29"/>
+      <c r="DB54" s="29"/>
     </row>
     <row r="55" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A55" s="10" t="s">
@@ -10193,10 +10257,11 @@
       <c r="CU55" s="3"/>
       <c r="CV55" s="3"/>
       <c r="CW55" s="3"/>
-      <c r="CX55" s="26"/>
+      <c r="CX55" s="3"/>
       <c r="CY55" s="26"/>
       <c r="CZ55" s="26"/>
       <c r="DA55" s="26"/>
+      <c r="DB55" s="26"/>
     </row>
     <row r="56" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="7"/>
@@ -10299,11 +10364,11 @@
       <c r="CU56" s="7"/>
       <c r="CV56" s="7"/>
       <c r="CW56" s="7"/>
-      <c r="CX56" s="6"/>
+      <c r="CX56" s="7"/>
       <c r="CY56" s="6"/>
       <c r="CZ56" s="6"/>
       <c r="DA56" s="6"/>
-      <c r="DB56" s="20"/>
+      <c r="DB56" s="6"/>
       <c r="DC56" s="20"/>
       <c r="DD56" s="20"/>
       <c r="DE56" s="20"/>
@@ -10475,11 +10540,11 @@
       <c r="CU57" s="7"/>
       <c r="CV57" s="7"/>
       <c r="CW57" s="7"/>
-      <c r="CX57" s="6"/>
+      <c r="CX57" s="7"/>
       <c r="CY57" s="6"/>
       <c r="CZ57" s="6"/>
       <c r="DA57" s="6"/>
-      <c r="DB57" s="20"/>
+      <c r="DB57" s="6"/>
       <c r="DC57" s="20"/>
       <c r="DD57" s="20"/>
       <c r="DE57" s="20"/>
@@ -10654,10 +10719,11 @@
       <c r="CU58" s="3"/>
       <c r="CV58" s="3"/>
       <c r="CW58" s="3"/>
-      <c r="CX58" s="26"/>
+      <c r="CX58" s="3"/>
       <c r="CY58" s="26"/>
       <c r="CZ58" s="26"/>
       <c r="DA58" s="26"/>
+      <c r="DB58" s="26"/>
     </row>
     <row r="59" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
@@ -10763,14 +10829,15 @@
       <c r="CU59" s="3"/>
       <c r="CV59" s="3"/>
       <c r="CW59" s="3"/>
-      <c r="CX59" s="26"/>
+      <c r="CX59" s="3"/>
       <c r="CY59" s="26"/>
       <c r="CZ59" s="26"/>
       <c r="DA59" s="26"/>
+      <c r="DB59" s="26"/>
     </row>
     <row r="60" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -10872,10 +10939,11 @@
       <c r="CU60" s="3"/>
       <c r="CV60" s="3"/>
       <c r="CW60" s="3"/>
-      <c r="CX60" s="26"/>
+      <c r="CX60" s="3"/>
       <c r="CY60" s="26"/>
       <c r="CZ60" s="26"/>
       <c r="DA60" s="26"/>
+      <c r="DB60" s="26"/>
     </row>
     <row r="61" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A61" s="3"/>
@@ -10979,10 +11047,11 @@
       <c r="CU61" s="3"/>
       <c r="CV61" s="3"/>
       <c r="CW61" s="3"/>
-      <c r="CX61" s="26"/>
+      <c r="CX61" s="3"/>
       <c r="CY61" s="26"/>
       <c r="CZ61" s="26"/>
       <c r="DA61" s="26"/>
+      <c r="DB61" s="26"/>
     </row>
     <row r="62" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
@@ -11088,14 +11157,15 @@
       <c r="CU62" s="3"/>
       <c r="CV62" s="3"/>
       <c r="CW62" s="3"/>
-      <c r="CX62" s="26"/>
+      <c r="CX62" s="3"/>
       <c r="CY62" s="26"/>
       <c r="CZ62" s="26"/>
       <c r="DA62" s="26"/>
+      <c r="DB62" s="26"/>
     </row>
     <row r="63" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -11197,10 +11267,11 @@
       <c r="CU63" s="3"/>
       <c r="CV63" s="3"/>
       <c r="CW63" s="3"/>
-      <c r="CX63" s="26"/>
+      <c r="CX63" s="3"/>
       <c r="CY63" s="26"/>
       <c r="CZ63" s="26"/>
       <c r="DA63" s="26"/>
+      <c r="DB63" s="26"/>
     </row>
     <row r="64" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
@@ -11306,10 +11377,11 @@
       <c r="CU64" s="3"/>
       <c r="CV64" s="3"/>
       <c r="CW64" s="3"/>
-      <c r="CX64" s="26"/>
+      <c r="CX64" s="3"/>
       <c r="CY64" s="26"/>
       <c r="CZ64" s="26"/>
       <c r="DA64" s="26"/>
+      <c r="DB64" s="26"/>
     </row>
     <row r="65" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A65" s="3"/>
@@ -11413,10 +11485,11 @@
       <c r="CU65" s="3"/>
       <c r="CV65" s="3"/>
       <c r="CW65" s="3"/>
-      <c r="CX65" s="26"/>
+      <c r="CX65" s="3"/>
       <c r="CY65" s="26"/>
       <c r="CZ65" s="26"/>
       <c r="DA65" s="26"/>
+      <c r="DB65" s="26"/>
     </row>
     <row r="66" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A66" s="13"/>
@@ -11570,10 +11643,13 @@
       <c r="CU66" s="25"/>
       <c r="CV66" s="25"/>
       <c r="CW66" s="25"/>
-      <c r="CX66" s="27"/>
+      <c r="CX66" s="25" t="s">
+        <v>53</v>
+      </c>
       <c r="CY66" s="27"/>
       <c r="CZ66" s="27"/>
       <c r="DA66" s="27"/>
+      <c r="DB66" s="27"/>
     </row>
     <row r="67" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
@@ -11879,10 +11955,13 @@
       <c r="CW67" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="CX67" s="28"/>
+      <c r="CX67" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="CY67" s="28"/>
       <c r="CZ67" s="28"/>
       <c r="DA67" s="28"/>
+      <c r="DB67" s="28"/>
     </row>
     <row r="68" spans="1:179" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="5"/>
@@ -11986,10 +12065,11 @@
       <c r="CU68" s="3"/>
       <c r="CV68" s="3"/>
       <c r="CW68" s="3"/>
-      <c r="CX68" s="26"/>
+      <c r="CX68" s="3"/>
       <c r="CY68" s="26"/>
       <c r="CZ68" s="26"/>
       <c r="DA68" s="26"/>
+      <c r="DB68" s="26"/>
     </row>
     <row r="69" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="24" t="s">
@@ -12295,11 +12375,13 @@
       <c r="CW69" s="12">
         <v>9.5886170407569011</v>
       </c>
-      <c r="CX69" s="14"/>
+      <c r="CX69" s="12">
+        <v>3.9349019577467033</v>
+      </c>
       <c r="CY69" s="14"/>
       <c r="CZ69" s="14"/>
       <c r="DA69" s="14"/>
-      <c r="DB69" s="20"/>
+      <c r="DB69" s="14"/>
       <c r="DC69" s="20"/>
       <c r="DD69" s="20"/>
       <c r="DE69" s="20"/>
@@ -12674,11 +12756,13 @@
       <c r="CW70" s="12">
         <v>4.081008142000158</v>
       </c>
-      <c r="CX70" s="14"/>
+      <c r="CX70" s="12">
+        <v>3.884177735188004</v>
+      </c>
       <c r="CY70" s="14"/>
       <c r="CZ70" s="14"/>
       <c r="DA70" s="14"/>
-      <c r="DB70" s="20"/>
+      <c r="DB70" s="14"/>
       <c r="DC70" s="20"/>
       <c r="DD70" s="20"/>
       <c r="DE70" s="20"/>
@@ -12850,11 +12934,11 @@
       <c r="CU71" s="7"/>
       <c r="CV71" s="7"/>
       <c r="CW71" s="7"/>
-      <c r="CX71" s="6"/>
+      <c r="CX71" s="7"/>
       <c r="CY71" s="6"/>
       <c r="CZ71" s="6"/>
       <c r="DA71" s="6"/>
-      <c r="DB71" s="20"/>
+      <c r="DB71" s="6"/>
       <c r="DC71" s="20"/>
       <c r="DD71" s="20"/>
       <c r="DE71" s="20"/>
@@ -13229,11 +13313,13 @@
       <c r="CW72" s="12">
         <v>7.5833165264184146</v>
       </c>
-      <c r="CX72" s="14"/>
+      <c r="CX72" s="12">
+        <v>3.9130106477429365</v>
+      </c>
       <c r="CY72" s="14"/>
       <c r="CZ72" s="14"/>
       <c r="DA72" s="14"/>
-      <c r="DB72" s="20"/>
+      <c r="DB72" s="14"/>
       <c r="DC72" s="20"/>
       <c r="DD72" s="20"/>
       <c r="DE72" s="20"/>
@@ -13406,10 +13492,11 @@
       <c r="CU73" s="9"/>
       <c r="CV73" s="9"/>
       <c r="CW73" s="9"/>
-      <c r="CX73" s="29"/>
+      <c r="CX73" s="9"/>
       <c r="CY73" s="29"/>
       <c r="CZ73" s="29"/>
       <c r="DA73" s="29"/>
+      <c r="DB73" s="29"/>
     </row>
     <row r="74" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A74" s="10" t="s">
@@ -13515,10 +13602,11 @@
       <c r="CU74" s="3"/>
       <c r="CV74" s="3"/>
       <c r="CW74" s="3"/>
-      <c r="CX74" s="26"/>
+      <c r="CX74" s="3"/>
       <c r="CY74" s="26"/>
       <c r="CZ74" s="26"/>
       <c r="DA74" s="26"/>
+      <c r="DB74" s="26"/>
     </row>
     <row r="75" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="7"/>
@@ -13621,11 +13709,11 @@
       <c r="CU75" s="20"/>
       <c r="CV75" s="20"/>
       <c r="CW75" s="20"/>
-      <c r="CX75" s="19"/>
+      <c r="CX75" s="20"/>
       <c r="CY75" s="19"/>
       <c r="CZ75" s="19"/>
       <c r="DA75" s="19"/>
-      <c r="DB75" s="20"/>
+      <c r="DB75" s="19"/>
       <c r="DC75" s="20"/>
       <c r="DD75" s="20"/>
       <c r="DE75" s="20"/>
@@ -13801,7 +13889,7 @@
       <c r="CY76" s="6"/>
       <c r="CZ76" s="6"/>
       <c r="DA76" s="6"/>
-      <c r="DB76" s="20"/>
+      <c r="DB76" s="6"/>
       <c r="DC76" s="20"/>
       <c r="DD76" s="20"/>
       <c r="DE76" s="20"/>
@@ -13984,10 +14072,11 @@
       <c r="CY77" s="26"/>
       <c r="CZ77" s="26"/>
       <c r="DA77" s="26"/>
+      <c r="DB77" s="26"/>
     </row>
     <row r="78" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -14093,6 +14182,7 @@
       <c r="CY78" s="26"/>
       <c r="CZ78" s="26"/>
       <c r="DA78" s="26"/>
+      <c r="DB78" s="26"/>
     </row>
     <row r="79" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A79" s="3"/>
@@ -14200,6 +14290,7 @@
       <c r="CY79" s="26"/>
       <c r="CZ79" s="26"/>
       <c r="DA79" s="26"/>
+      <c r="DB79" s="26"/>
     </row>
     <row r="80" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
@@ -14309,10 +14400,11 @@
       <c r="CY80" s="26"/>
       <c r="CZ80" s="26"/>
       <c r="DA80" s="26"/>
+      <c r="DB80" s="26"/>
     </row>
     <row r="81" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -14418,6 +14510,7 @@
       <c r="CY81" s="26"/>
       <c r="CZ81" s="26"/>
       <c r="DA81" s="26"/>
+      <c r="DB81" s="26"/>
     </row>
     <row r="82" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
@@ -14527,6 +14620,7 @@
       <c r="CY82" s="26"/>
       <c r="CZ82" s="26"/>
       <c r="DA82" s="26"/>
+      <c r="DB82" s="26"/>
     </row>
     <row r="83" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A83" s="3"/>
@@ -14634,6 +14728,7 @@
       <c r="CY83" s="3"/>
       <c r="CZ83" s="3"/>
       <c r="DA83" s="3"/>
+      <c r="DB83" s="3"/>
     </row>
     <row r="84" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A84" s="13"/>
@@ -14793,6 +14888,9 @@
       <c r="CY84" s="25"/>
       <c r="CZ84" s="25"/>
       <c r="DA84" s="25"/>
+      <c r="DB84" s="25">
+        <v>2026</v>
+      </c>
     </row>
     <row r="85" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
@@ -15109,6 +15207,9 @@
       </c>
       <c r="DA85" s="11" t="s">
         <v>5</v>
+      </c>
+      <c r="DB85" s="11" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:179" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -15217,6 +15318,7 @@
       <c r="CY86" s="3"/>
       <c r="CZ86" s="3"/>
       <c r="DA86" s="3"/>
+      <c r="DB86" s="3"/>
     </row>
     <row r="87" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="24" t="s">
@@ -15534,7 +15636,9 @@
       <c r="DA87" s="12">
         <v>118.03028529977399</v>
       </c>
-      <c r="DB87" s="20"/>
+      <c r="DB87" s="12">
+        <v>119.46591334378152</v>
+      </c>
       <c r="DC87" s="20"/>
       <c r="DD87" s="20"/>
       <c r="DE87" s="20"/>
@@ -15925,7 +16029,9 @@
       <c r="DA88" s="12">
         <v>128.59510954066781</v>
       </c>
-      <c r="DB88" s="20"/>
+      <c r="DB88" s="12">
+        <v>132.63885488879382</v>
+      </c>
       <c r="DC88" s="20"/>
       <c r="DD88" s="20"/>
       <c r="DE88" s="20"/>
@@ -16105,7 +16211,7 @@
       <c r="CY89" s="7"/>
       <c r="CZ89" s="7"/>
       <c r="DA89" s="7"/>
-      <c r="DB89" s="20"/>
+      <c r="DB89" s="7"/>
       <c r="DC89" s="20"/>
       <c r="DD89" s="20"/>
       <c r="DE89" s="20"/>
@@ -16496,7 +16602,9 @@
       <c r="DA90" s="12">
         <v>121.75167550730966</v>
       </c>
-      <c r="DB90" s="20"/>
+      <c r="DB90" s="12">
+        <v>125.14944908211139</v>
+      </c>
       <c r="DC90" s="20"/>
       <c r="DD90" s="20"/>
       <c r="DE90" s="20"/>
@@ -16677,6 +16785,7 @@
       <c r="CY91" s="9"/>
       <c r="CZ91" s="9"/>
       <c r="DA91" s="9"/>
+      <c r="DB91" s="9"/>
     </row>
     <row r="92" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A92" s="10" t="s">
@@ -16786,6 +16895,7 @@
       <c r="CY92" s="3"/>
       <c r="CZ92" s="3"/>
       <c r="DA92" s="3"/>
+      <c r="DB92" s="3"/>
     </row>
     <row r="93" spans="1:179" x14ac:dyDescent="0.25">
       <c r="B93" s="3"/>
@@ -16892,6 +17002,7 @@
       <c r="CY93" s="3"/>
       <c r="CZ93" s="3"/>
       <c r="DA93" s="3"/>
+      <c r="DB93" s="3"/>
     </row>
     <row r="94" spans="1:179" x14ac:dyDescent="0.25">
       <c r="B94" s="3"/>
@@ -16998,6 +17109,7 @@
       <c r="CY94" s="3"/>
       <c r="CZ94" s="3"/>
       <c r="DA94" s="3"/>
+      <c r="DB94" s="3"/>
     </row>
     <row r="95" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
@@ -17107,6 +17219,7 @@
       <c r="CY95" s="3"/>
       <c r="CZ95" s="3"/>
       <c r="DA95" s="3"/>
+      <c r="DB95" s="3"/>
     </row>
     <row r="96" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
@@ -17216,10 +17329,11 @@
       <c r="CY96" s="3"/>
       <c r="CZ96" s="3"/>
       <c r="DA96" s="3"/>
+      <c r="DB96" s="3"/>
     </row>
     <row r="97" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -17325,6 +17439,7 @@
       <c r="CY97" s="3"/>
       <c r="CZ97" s="3"/>
       <c r="DA97" s="3"/>
+      <c r="DB97" s="3"/>
     </row>
     <row r="98" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A98" s="3"/>
@@ -17432,6 +17547,7 @@
       <c r="CY98" s="3"/>
       <c r="CZ98" s="3"/>
       <c r="DA98" s="3"/>
+      <c r="DB98" s="3"/>
     </row>
     <row r="99" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
@@ -17541,10 +17657,11 @@
       <c r="CY99" s="3"/>
       <c r="CZ99" s="3"/>
       <c r="DA99" s="3"/>
+      <c r="DB99" s="3"/>
     </row>
     <row r="100" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -17650,6 +17767,7 @@
       <c r="CY100" s="3"/>
       <c r="CZ100" s="3"/>
       <c r="DA100" s="3"/>
+      <c r="DB100" s="3"/>
     </row>
     <row r="101" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
@@ -17759,6 +17877,7 @@
       <c r="CY101" s="3"/>
       <c r="CZ101" s="3"/>
       <c r="DA101" s="3"/>
+      <c r="DB101" s="3"/>
     </row>
     <row r="102" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A102" s="3"/>
@@ -17866,6 +17985,7 @@
       <c r="CY102" s="3"/>
       <c r="CZ102" s="3"/>
       <c r="DA102" s="3"/>
+      <c r="DB102" s="3"/>
     </row>
     <row r="103" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A103" s="13"/>
@@ -18025,6 +18145,9 @@
       <c r="CY103" s="25"/>
       <c r="CZ103" s="25"/>
       <c r="DA103" s="25"/>
+      <c r="DB103" s="25">
+        <v>2026</v>
+      </c>
     </row>
     <row r="104" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
@@ -18341,6 +18464,9 @@
       </c>
       <c r="DA104" s="11" t="s">
         <v>5</v>
+      </c>
+      <c r="DB104" s="11" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="105" spans="1:179" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -18449,6 +18575,7 @@
       <c r="CY105" s="3"/>
       <c r="CZ105" s="3"/>
       <c r="DA105" s="3"/>
+      <c r="DB105" s="3"/>
     </row>
     <row r="106" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="24" t="s">
@@ -18766,7 +18893,9 @@
       <c r="DA106" s="12">
         <v>62.795759746145841</v>
       </c>
-      <c r="DB106" s="20"/>
+      <c r="DB106" s="12">
+        <v>54.272479592168423</v>
+      </c>
       <c r="DC106" s="20"/>
       <c r="DD106" s="20"/>
       <c r="DE106" s="20"/>
@@ -19157,7 +19286,9 @@
       <c r="DA107" s="12">
         <v>37.204240253854152</v>
       </c>
-      <c r="DB107" s="20"/>
+      <c r="DB107" s="12">
+        <v>45.727520407831577</v>
+      </c>
       <c r="DC107" s="20"/>
       <c r="DD107" s="20"/>
       <c r="DE107" s="20"/>
@@ -19337,7 +19468,7 @@
       <c r="CY108" s="7"/>
       <c r="CZ108" s="7"/>
       <c r="DA108" s="7"/>
-      <c r="DB108" s="20"/>
+      <c r="DB108" s="7"/>
       <c r="DC108" s="20"/>
       <c r="DD108" s="20"/>
       <c r="DE108" s="20"/>
@@ -19728,7 +19859,9 @@
       <c r="DA109" s="12">
         <v>100</v>
       </c>
-      <c r="DB109" s="20"/>
+      <c r="DB109" s="12">
+        <v>100</v>
+      </c>
       <c r="DC109" s="20"/>
       <c r="DD109" s="20"/>
       <c r="DE109" s="20"/>
@@ -19909,6 +20042,7 @@
       <c r="CY110" s="9"/>
       <c r="CZ110" s="9"/>
       <c r="DA110" s="9"/>
+      <c r="DB110" s="9"/>
     </row>
     <row r="111" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A111" s="10" t="s">
@@ -20018,6 +20152,7 @@
       <c r="CY111" s="3"/>
       <c r="CZ111" s="3"/>
       <c r="DA111" s="3"/>
+      <c r="DB111" s="3"/>
     </row>
     <row r="112" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="7"/>
@@ -20124,7 +20259,7 @@
       <c r="CY112" s="7"/>
       <c r="CZ112" s="7"/>
       <c r="DA112" s="7"/>
-      <c r="DB112" s="20"/>
+      <c r="DB112" s="7"/>
       <c r="DC112" s="20"/>
       <c r="DD112" s="20"/>
       <c r="DE112" s="20"/>
@@ -20304,7 +20439,7 @@
       <c r="CY113" s="7"/>
       <c r="CZ113" s="7"/>
       <c r="DA113" s="7"/>
-      <c r="DB113" s="20"/>
+      <c r="DB113" s="7"/>
       <c r="DC113" s="20"/>
       <c r="DD113" s="20"/>
       <c r="DE113" s="20"/>
@@ -20487,6 +20622,7 @@
       <c r="CY114" s="3"/>
       <c r="CZ114" s="3"/>
       <c r="DA114" s="3"/>
+      <c r="DB114" s="3"/>
     </row>
     <row r="115" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
@@ -20596,10 +20732,11 @@
       <c r="CY115" s="3"/>
       <c r="CZ115" s="3"/>
       <c r="DA115" s="3"/>
+      <c r="DB115" s="3"/>
     </row>
     <row r="116" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -20705,6 +20842,7 @@
       <c r="CY116" s="3"/>
       <c r="CZ116" s="3"/>
       <c r="DA116" s="3"/>
+      <c r="DB116" s="3"/>
     </row>
     <row r="117" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A117" s="3"/>
@@ -20812,6 +20950,7 @@
       <c r="CY117" s="3"/>
       <c r="CZ117" s="3"/>
       <c r="DA117" s="3"/>
+      <c r="DB117" s="3"/>
     </row>
     <row r="118" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
@@ -20921,10 +21060,11 @@
       <c r="CY118" s="3"/>
       <c r="CZ118" s="3"/>
       <c r="DA118" s="3"/>
+      <c r="DB118" s="3"/>
     </row>
     <row r="119" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -21030,6 +21170,7 @@
       <c r="CY119" s="3"/>
       <c r="CZ119" s="3"/>
       <c r="DA119" s="3"/>
+      <c r="DB119" s="3"/>
     </row>
     <row r="120" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
@@ -21139,6 +21280,7 @@
       <c r="CY120" s="3"/>
       <c r="CZ120" s="3"/>
       <c r="DA120" s="3"/>
+      <c r="DB120" s="3"/>
     </row>
     <row r="121" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A121" s="3"/>
@@ -21246,6 +21388,7 @@
       <c r="CY121" s="3"/>
       <c r="CZ121" s="3"/>
       <c r="DA121" s="3"/>
+      <c r="DB121" s="3"/>
     </row>
     <row r="122" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A122" s="13"/>
@@ -21405,6 +21548,9 @@
       <c r="CY122" s="25"/>
       <c r="CZ122" s="25"/>
       <c r="DA122" s="25"/>
+      <c r="DB122" s="25">
+        <v>2026</v>
+      </c>
     </row>
     <row r="123" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A123" s="4" t="s">
@@ -21721,6 +21867,9 @@
       </c>
       <c r="DA123" s="11" t="s">
         <v>5</v>
+      </c>
+      <c r="DB123" s="11" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="124" spans="1:179" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -21829,6 +21978,7 @@
       <c r="CY124" s="3"/>
       <c r="CZ124" s="3"/>
       <c r="DA124" s="3"/>
+      <c r="DB124" s="3"/>
     </row>
     <row r="125" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="24" t="s">
@@ -22146,7 +22296,9 @@
       <c r="DA125" s="12">
         <v>64.775654353708205</v>
       </c>
-      <c r="DB125" s="20"/>
+      <c r="DB125" s="12">
+        <v>56.854467782240903</v>
+      </c>
       <c r="DC125" s="20"/>
       <c r="DD125" s="20"/>
       <c r="DE125" s="20"/>
@@ -22537,7 +22689,9 @@
       <c r="DA126" s="12">
         <v>35.224345646291802</v>
       </c>
-      <c r="DB126" s="20"/>
+      <c r="DB126" s="12">
+        <v>43.14553221775909</v>
+      </c>
       <c r="DC126" s="20"/>
       <c r="DD126" s="20"/>
       <c r="DE126" s="20"/>
@@ -22717,7 +22871,7 @@
       <c r="CY127" s="7"/>
       <c r="CZ127" s="7"/>
       <c r="DA127" s="7"/>
-      <c r="DB127" s="20"/>
+      <c r="DB127" s="7"/>
       <c r="DC127" s="20"/>
       <c r="DD127" s="20"/>
       <c r="DE127" s="20"/>
@@ -23108,7 +23262,9 @@
       <c r="DA128" s="12">
         <v>100</v>
       </c>
-      <c r="DB128" s="20"/>
+      <c r="DB128" s="12">
+        <v>100</v>
+      </c>
       <c r="DC128" s="20"/>
       <c r="DD128" s="20"/>
       <c r="DE128" s="20"/>
@@ -23183,7 +23339,7 @@
       <c r="FV128" s="20"/>
       <c r="FW128" s="20"/>
     </row>
-    <row r="129" spans="1:105" s="17" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:106" s="17" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="9"/>
       <c r="B129" s="9"/>
       <c r="C129" s="9"/>
@@ -23289,8 +23445,9 @@
       <c r="CY129" s="9"/>
       <c r="CZ129" s="9"/>
       <c r="DA129" s="9"/>
+      <c r="DB129" s="9"/>
     </row>
-    <row r="130" spans="1:105" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:106" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A130" s="10" t="s">
         <v>6</v>
       </c>
@@ -23398,14 +23555,16 @@
       <c r="CY130" s="3"/>
       <c r="CZ130" s="3"/>
       <c r="DA130" s="3"/>
+      <c r="DB130" s="3"/>
     </row>
-    <row r="131" spans="1:105" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:106" x14ac:dyDescent="0.25">
       <c r="CX131" s="22"/>
       <c r="CY131" s="22"/>
       <c r="CZ131" s="22"/>
       <c r="DA131" s="22"/>
+      <c r="DB131" s="22"/>
     </row>
-    <row r="132" spans="1:105" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:106" x14ac:dyDescent="0.25">
       <c r="CT132" s="23"/>
       <c r="CU132" s="23"/>
       <c r="CV132" s="23"/>
@@ -23413,8 +23572,9 @@
       <c r="CY132" s="23"/>
       <c r="CZ132" s="23"/>
       <c r="DA132" s="23"/>
+      <c r="DB132" s="23"/>
     </row>
-    <row r="133" spans="1:105" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:106" x14ac:dyDescent="0.25">
       <c r="CT133" s="23"/>
       <c r="CU133" s="23"/>
       <c r="CV133" s="23"/>
@@ -23422,8 +23582,9 @@
       <c r="CY133" s="23"/>
       <c r="CZ133" s="23"/>
       <c r="DA133" s="23"/>
+      <c r="DB133" s="23"/>
     </row>
-    <row r="134" spans="1:105" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:106" x14ac:dyDescent="0.25">
       <c r="CT134" s="23"/>
       <c r="CU134" s="23"/>
       <c r="CV134" s="23"/>
@@ -23431,8 +23592,9 @@
       <c r="CY134" s="23"/>
       <c r="CZ134" s="23"/>
       <c r="DA134" s="23"/>
+      <c r="DB134" s="23"/>
     </row>
-    <row r="135" spans="1:105" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:106" x14ac:dyDescent="0.25">
       <c r="CT135" s="23"/>
       <c r="CU135" s="23"/>
       <c r="CV135" s="23"/>
@@ -23440,8 +23602,9 @@
       <c r="CY135" s="23"/>
       <c r="CZ135" s="23"/>
       <c r="DA135" s="23"/>
+      <c r="DB135" s="23"/>
     </row>
-    <row r="136" spans="1:105" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:106" x14ac:dyDescent="0.25">
       <c r="CT136" s="23"/>
       <c r="CU136" s="23"/>
       <c r="CV136" s="23"/>
@@ -23449,6 +23612,7 @@
       <c r="CY136" s="23"/>
       <c r="CZ136" s="23"/>
       <c r="DA136" s="23"/>
+      <c r="DB136" s="23"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
@@ -23456,9 +23620,9 @@
   <pageSetup paperSize="9" scale="47" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="38" max="81" man="1"/>
-    <brk id="76" max="81" man="1"/>
-    <brk id="94" max="81" man="1"/>
+    <brk id="38" max="105" man="1"/>
+    <brk id="76" max="105" man="1"/>
+    <brk id="94" max="105" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
--- a/Data/National Accounts/PSA-21OS_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-21OS_2018PSNA_Qrt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of August 2026\Tables\NAP Q1 2000 to Q2 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FF9D2FF-874D-4C6B-BDC3-232DD561DEEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF72708D-6CA5-436F-960E-78BAF2BAA01E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
@@ -356,7 +356,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">OS!$A$1:$DB$131</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">OS!$A$1:$DC$131</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -530,7 +530,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="54">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -685,13 +685,13 @@
     <t>Table 22.7 Gross Value Added in Other Services, by Industry</t>
   </si>
   <si>
-    <t>As of May 2026</t>
+    <t>2025 - 2026</t>
   </si>
   <si>
-    <t>Q1 2000 to Q1 2026</t>
+    <t>As of August 2026</t>
   </si>
   <si>
-    <t>2025 - 2026</t>
+    <t>Q1 2000 to Q2 2026</t>
   </si>
 </sst>
 </file>
@@ -1211,12 +1211,12 @@
   <sheetPr transitionEvaluation="1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:FW136"/>
+  <dimension ref="A1:FW137"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53.85546875" style="3" customWidth="1"/>
-    <col min="2" max="106" width="13" style="21" customWidth="1"/>
-    <col min="107" max="16384" width="10" style="21"/>
+    <col min="2" max="107" width="13" style="21" customWidth="1"/>
+    <col min="108" max="16384" width="10" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -1231,7 +1231,7 @@
     </row>
     <row r="3" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -1244,7 +1244,7 @@
     </row>
     <row r="6" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -1359,6 +1359,7 @@
       <c r="CZ8" s="3"/>
       <c r="DA8" s="3"/>
       <c r="DB8" s="3"/>
+      <c r="DC8" s="3"/>
     </row>
     <row r="9" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="13"/>
@@ -1521,6 +1522,7 @@
       <c r="DB9" s="25">
         <v>2026</v>
       </c>
+      <c r="DC9" s="25"/>
     </row>
     <row r="10" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
@@ -1840,6 +1842,9 @@
       </c>
       <c r="DB10" s="11" t="s">
         <v>2</v>
+      </c>
+      <c r="DC10" s="11" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:179" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1949,6 +1954,7 @@
       <c r="CZ11" s="3"/>
       <c r="DA11" s="3"/>
       <c r="DB11" s="3"/>
+      <c r="DC11" s="3"/>
     </row>
     <row r="12" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="24" t="s">
@@ -2267,9 +2273,11 @@
         <v>107056.12581721888</v>
       </c>
       <c r="DB12" s="15">
-        <v>87385.601711987081</v>
-      </c>
-      <c r="DC12" s="20"/>
+        <v>86260.135908849566</v>
+      </c>
+      <c r="DC12" s="15">
+        <v>88470.27867137533</v>
+      </c>
       <c r="DD12" s="20"/>
       <c r="DE12" s="20"/>
       <c r="DF12" s="20"/>
@@ -2660,9 +2668,11 @@
         <v>63426.923117927676</v>
       </c>
       <c r="DB13" s="15">
-        <v>73627.129544531592</v>
-      </c>
-      <c r="DC13" s="20"/>
+        <v>73220.735864788716</v>
+      </c>
+      <c r="DC13" s="15">
+        <v>58849.975689242172</v>
+      </c>
       <c r="DD13" s="20"/>
       <c r="DE13" s="20"/>
       <c r="DF13" s="20"/>
@@ -2842,7 +2852,7 @@
       <c r="CZ14" s="16"/>
       <c r="DA14" s="16"/>
       <c r="DB14" s="16"/>
-      <c r="DC14" s="20"/>
+      <c r="DC14" s="16"/>
       <c r="DD14" s="20"/>
       <c r="DE14" s="20"/>
       <c r="DF14" s="20"/>
@@ -3233,9 +3243,11 @@
         <v>170483.04893514657</v>
       </c>
       <c r="DB15" s="16">
-        <v>161012.73125651869</v>
-      </c>
-      <c r="DC15" s="20"/>
+        <v>159480.8717736383</v>
+      </c>
+      <c r="DC15" s="16">
+        <v>147320.25436061749</v>
+      </c>
       <c r="DD15" s="20"/>
       <c r="DE15" s="20"/>
       <c r="DF15" s="20"/>
@@ -3416,6 +3428,7 @@
       <c r="CZ16" s="9"/>
       <c r="DA16" s="9"/>
       <c r="DB16" s="9"/>
+      <c r="DC16" s="9"/>
     </row>
     <row r="17" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
@@ -3526,6 +3539,7 @@
       <c r="CZ17" s="3"/>
       <c r="DA17" s="3"/>
       <c r="DB17" s="3"/>
+      <c r="DC17" s="3"/>
     </row>
     <row r="18" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="7"/>
@@ -3633,7 +3647,7 @@
       <c r="CZ18" s="7"/>
       <c r="DA18" s="7"/>
       <c r="DB18" s="7"/>
-      <c r="DC18" s="20"/>
+      <c r="DC18" s="7"/>
       <c r="DD18" s="20"/>
       <c r="DE18" s="20"/>
       <c r="DF18" s="20"/>
@@ -3813,7 +3827,7 @@
       <c r="CZ19" s="7"/>
       <c r="DA19" s="7"/>
       <c r="DB19" s="7"/>
-      <c r="DC19" s="20"/>
+      <c r="DC19" s="7"/>
       <c r="DD19" s="20"/>
       <c r="DE19" s="20"/>
       <c r="DF19" s="20"/>
@@ -3996,6 +4010,7 @@
       <c r="CZ20" s="3"/>
       <c r="DA20" s="3"/>
       <c r="DB20" s="3"/>
+      <c r="DC20" s="3"/>
     </row>
     <row r="21" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
@@ -4106,10 +4121,11 @@
       <c r="CZ21" s="3"/>
       <c r="DA21" s="3"/>
       <c r="DB21" s="3"/>
+      <c r="DC21" s="3"/>
     </row>
     <row r="22" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -4216,6 +4232,7 @@
       <c r="CZ22" s="3"/>
       <c r="DA22" s="3"/>
       <c r="DB22" s="3"/>
+      <c r="DC22" s="3"/>
     </row>
     <row r="23" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="3"/>
@@ -4324,6 +4341,7 @@
       <c r="CZ23" s="3"/>
       <c r="DA23" s="3"/>
       <c r="DB23" s="3"/>
+      <c r="DC23" s="3"/>
     </row>
     <row r="24" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
@@ -4434,10 +4452,11 @@
       <c r="CZ24" s="3"/>
       <c r="DA24" s="3"/>
       <c r="DB24" s="3"/>
+      <c r="DC24" s="3"/>
     </row>
     <row r="25" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -4544,6 +4563,7 @@
       <c r="CZ25" s="3"/>
       <c r="DA25" s="3"/>
       <c r="DB25" s="3"/>
+      <c r="DC25" s="3"/>
     </row>
     <row r="26" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
@@ -4654,6 +4674,7 @@
       <c r="CZ26" s="3"/>
       <c r="DA26" s="3"/>
       <c r="DB26" s="3"/>
+      <c r="DC26" s="3"/>
     </row>
     <row r="27" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="3"/>
@@ -4762,6 +4783,7 @@
       <c r="CZ27" s="3"/>
       <c r="DA27" s="3"/>
       <c r="DB27" s="3"/>
+      <c r="DC27" s="3"/>
     </row>
     <row r="28" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A28" s="13"/>
@@ -4924,6 +4946,7 @@
       <c r="DB28" s="25">
         <v>2026</v>
       </c>
+      <c r="DC28" s="25"/>
     </row>
     <row r="29" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
@@ -5243,6 +5266,9 @@
       </c>
       <c r="DB29" s="11" t="s">
         <v>2</v>
+      </c>
+      <c r="DC29" s="11" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:179" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -5352,6 +5378,7 @@
       <c r="CZ30" s="3"/>
       <c r="DA30" s="3"/>
       <c r="DB30" s="3"/>
+      <c r="DC30" s="3"/>
     </row>
     <row r="31" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="24" t="s">
@@ -5670,9 +5697,11 @@
         <v>90702.251159791005</v>
       </c>
       <c r="DB31" s="15">
-        <v>73146.891247984342</v>
-      </c>
-      <c r="DC31" s="20"/>
+        <v>72204.810137451306</v>
+      </c>
+      <c r="DC31" s="15">
+        <v>72704.259584968328</v>
+      </c>
       <c r="DD31" s="20"/>
       <c r="DE31" s="20"/>
       <c r="DF31" s="20"/>
@@ -6063,9 +6092,11 @@
         <v>49322.966747712213</v>
       </c>
       <c r="DB32" s="15">
-        <v>55509.473152690858</v>
-      </c>
-      <c r="DC32" s="20"/>
+        <v>55204.324702241152</v>
+      </c>
+      <c r="DC32" s="15">
+        <v>45606.573350598483</v>
+      </c>
       <c r="DD32" s="20"/>
       <c r="DE32" s="20"/>
       <c r="DF32" s="20"/>
@@ -6245,7 +6276,7 @@
       <c r="CZ33" s="16"/>
       <c r="DA33" s="16"/>
       <c r="DB33" s="16"/>
-      <c r="DC33" s="20"/>
+      <c r="DC33" s="16"/>
       <c r="DD33" s="20"/>
       <c r="DE33" s="20"/>
       <c r="DF33" s="20"/>
@@ -6636,9 +6667,11 @@
         <v>140025.21790750322</v>
       </c>
       <c r="DB34" s="16">
-        <v>128656.3644006752</v>
-      </c>
-      <c r="DC34" s="20"/>
+        <v>127409.13483969246</v>
+      </c>
+      <c r="DC34" s="16">
+        <v>118310.83293556681</v>
+      </c>
       <c r="DD34" s="20"/>
       <c r="DE34" s="20"/>
       <c r="DF34" s="20"/>
@@ -6819,6 +6852,7 @@
       <c r="CZ35" s="9"/>
       <c r="DA35" s="9"/>
       <c r="DB35" s="9"/>
+      <c r="DC35" s="9"/>
     </row>
     <row r="36" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="10" t="s">
@@ -6929,6 +6963,7 @@
       <c r="CZ36" s="3"/>
       <c r="DA36" s="3"/>
       <c r="DB36" s="3"/>
+      <c r="DC36" s="3"/>
     </row>
     <row r="37" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="7"/>
@@ -7036,7 +7071,7 @@
       <c r="CZ37" s="6"/>
       <c r="DA37" s="6"/>
       <c r="DB37" s="6"/>
-      <c r="DC37" s="20"/>
+      <c r="DC37" s="6"/>
       <c r="DD37" s="20"/>
       <c r="DE37" s="20"/>
       <c r="DF37" s="20"/>
@@ -7216,7 +7251,7 @@
       <c r="CZ38" s="6"/>
       <c r="DA38" s="6"/>
       <c r="DB38" s="6"/>
-      <c r="DC38" s="20"/>
+      <c r="DC38" s="6"/>
       <c r="DD38" s="20"/>
       <c r="DE38" s="20"/>
       <c r="DF38" s="20"/>
@@ -7399,6 +7434,7 @@
       <c r="CZ39" s="26"/>
       <c r="DA39" s="26"/>
       <c r="DB39" s="26"/>
+      <c r="DC39" s="26"/>
     </row>
     <row r="40" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
@@ -7509,10 +7545,11 @@
       <c r="CZ40" s="26"/>
       <c r="DA40" s="26"/>
       <c r="DB40" s="26"/>
+      <c r="DC40" s="26"/>
     </row>
     <row r="41" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -7619,6 +7656,7 @@
       <c r="CZ41" s="26"/>
       <c r="DA41" s="26"/>
       <c r="DB41" s="26"/>
+      <c r="DC41" s="26"/>
     </row>
     <row r="42" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="3"/>
@@ -7727,6 +7765,7 @@
       <c r="CZ42" s="26"/>
       <c r="DA42" s="26"/>
       <c r="DB42" s="26"/>
+      <c r="DC42" s="26"/>
     </row>
     <row r="43" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
@@ -7837,10 +7876,11 @@
       <c r="CZ43" s="26"/>
       <c r="DA43" s="26"/>
       <c r="DB43" s="26"/>
+      <c r="DC43" s="26"/>
     </row>
     <row r="44" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -7947,6 +7987,7 @@
       <c r="CZ44" s="26"/>
       <c r="DA44" s="26"/>
       <c r="DB44" s="26"/>
+      <c r="DC44" s="26"/>
     </row>
     <row r="45" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
@@ -8036,6 +8077,7 @@
       <c r="CZ45" s="18"/>
       <c r="DA45" s="18"/>
       <c r="DB45" s="18"/>
+      <c r="DC45" s="18"/>
     </row>
     <row r="46" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="3"/>
@@ -8139,11 +8181,12 @@
       <c r="CU46" s="3"/>
       <c r="CV46" s="3"/>
       <c r="CW46" s="3"/>
-      <c r="CX46" s="26"/>
-      <c r="CY46" s="26"/>
+      <c r="CX46" s="3"/>
+      <c r="CY46" s="3"/>
       <c r="CZ46" s="26"/>
       <c r="DA46" s="26"/>
       <c r="DB46" s="26"/>
+      <c r="DC46" s="26"/>
     </row>
     <row r="47" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A47" s="13"/>
@@ -8298,12 +8341,13 @@
       <c r="CV47" s="25"/>
       <c r="CW47" s="25"/>
       <c r="CX47" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="CY47" s="27"/>
+        <v>51</v>
+      </c>
+      <c r="CY47" s="25"/>
       <c r="CZ47" s="27"/>
       <c r="DA47" s="27"/>
       <c r="DB47" s="27"/>
+      <c r="DC47" s="27"/>
     </row>
     <row r="48" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
@@ -8612,10 +8656,13 @@
       <c r="CX48" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="CY48" s="28"/>
+      <c r="CY48" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ48" s="28"/>
       <c r="DA48" s="28"/>
       <c r="DB48" s="28"/>
+      <c r="DC48" s="28"/>
     </row>
     <row r="49" spans="1:175" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="5"/>
@@ -8720,10 +8767,11 @@
       <c r="CV49" s="3"/>
       <c r="CW49" s="3"/>
       <c r="CX49" s="3"/>
-      <c r="CY49" s="26"/>
+      <c r="CY49" s="3"/>
       <c r="CZ49" s="26"/>
       <c r="DA49" s="26"/>
       <c r="DB49" s="26"/>
+      <c r="DC49" s="26"/>
     </row>
     <row r="50" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="24" t="s">
@@ -9030,13 +9078,15 @@
         <v>11.773062025790409</v>
       </c>
       <c r="CX50" s="12">
-        <v>7.9131304137421097</v>
-      </c>
-      <c r="CY50" s="14"/>
+        <v>6.5232843108282879</v>
+      </c>
+      <c r="CY50" s="12">
+        <v>5.5563696785761323</v>
+      </c>
       <c r="CZ50" s="14"/>
       <c r="DA50" s="14"/>
       <c r="DB50" s="14"/>
-      <c r="DC50" s="20"/>
+      <c r="DC50" s="14"/>
       <c r="DD50" s="20"/>
       <c r="DE50" s="20"/>
       <c r="DF50" s="20"/>
@@ -9411,13 +9461,15 @@
         <v>6.5876396048526971</v>
       </c>
       <c r="CX51" s="12">
-        <v>7.0389565674121997</v>
-      </c>
-      <c r="CY51" s="14"/>
+        <v>6.4481423430309661</v>
+      </c>
+      <c r="CY51" s="12">
+        <v>6.5830233846833011</v>
+      </c>
       <c r="CZ51" s="14"/>
       <c r="DA51" s="14"/>
       <c r="DB51" s="14"/>
-      <c r="DC51" s="20"/>
+      <c r="DC51" s="14"/>
       <c r="DD51" s="20"/>
       <c r="DE51" s="20"/>
       <c r="DF51" s="20"/>
@@ -9590,11 +9642,11 @@
       <c r="CV52" s="7"/>
       <c r="CW52" s="7"/>
       <c r="CX52" s="7"/>
-      <c r="CY52" s="6"/>
+      <c r="CY52" s="7"/>
       <c r="CZ52" s="6"/>
       <c r="DA52" s="6"/>
       <c r="DB52" s="6"/>
-      <c r="DC52" s="20"/>
+      <c r="DC52" s="6"/>
       <c r="DD52" s="20"/>
       <c r="DE52" s="20"/>
       <c r="DF52" s="20"/>
@@ -9969,13 +10021,15 @@
         <v>9.7859762941474315</v>
       </c>
       <c r="CX53" s="12">
-        <v>7.5116271967010846</v>
-      </c>
-      <c r="CY53" s="14"/>
+        <v>6.4887720202443546</v>
+      </c>
+      <c r="CY53" s="12">
+        <v>5.9641051984317386</v>
+      </c>
       <c r="CZ53" s="14"/>
       <c r="DA53" s="14"/>
       <c r="DB53" s="14"/>
-      <c r="DC53" s="20"/>
+      <c r="DC53" s="14"/>
       <c r="DD53" s="20"/>
       <c r="DE53" s="20"/>
       <c r="DF53" s="20"/>
@@ -10148,10 +10202,11 @@
       <c r="CV54" s="9"/>
       <c r="CW54" s="9"/>
       <c r="CX54" s="9"/>
-      <c r="CY54" s="29"/>
+      <c r="CY54" s="9"/>
       <c r="CZ54" s="29"/>
       <c r="DA54" s="29"/>
       <c r="DB54" s="29"/>
+      <c r="DC54" s="29"/>
     </row>
     <row r="55" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A55" s="10" t="s">
@@ -10258,10 +10313,11 @@
       <c r="CV55" s="3"/>
       <c r="CW55" s="3"/>
       <c r="CX55" s="3"/>
-      <c r="CY55" s="26"/>
+      <c r="CY55" s="3"/>
       <c r="CZ55" s="26"/>
       <c r="DA55" s="26"/>
       <c r="DB55" s="26"/>
+      <c r="DC55" s="26"/>
     </row>
     <row r="56" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="7"/>
@@ -10365,11 +10421,11 @@
       <c r="CV56" s="7"/>
       <c r="CW56" s="7"/>
       <c r="CX56" s="7"/>
-      <c r="CY56" s="6"/>
+      <c r="CY56" s="7"/>
       <c r="CZ56" s="6"/>
       <c r="DA56" s="6"/>
       <c r="DB56" s="6"/>
-      <c r="DC56" s="20"/>
+      <c r="DC56" s="6"/>
       <c r="DD56" s="20"/>
       <c r="DE56" s="20"/>
       <c r="DF56" s="20"/>
@@ -10541,11 +10597,11 @@
       <c r="CV57" s="7"/>
       <c r="CW57" s="7"/>
       <c r="CX57" s="7"/>
-      <c r="CY57" s="6"/>
+      <c r="CY57" s="7"/>
       <c r="CZ57" s="6"/>
       <c r="DA57" s="6"/>
       <c r="DB57" s="6"/>
-      <c r="DC57" s="20"/>
+      <c r="DC57" s="6"/>
       <c r="DD57" s="20"/>
       <c r="DE57" s="20"/>
       <c r="DF57" s="20"/>
@@ -10720,10 +10776,11 @@
       <c r="CV58" s="3"/>
       <c r="CW58" s="3"/>
       <c r="CX58" s="3"/>
-      <c r="CY58" s="26"/>
+      <c r="CY58" s="3"/>
       <c r="CZ58" s="26"/>
       <c r="DA58" s="26"/>
       <c r="DB58" s="26"/>
+      <c r="DC58" s="26"/>
     </row>
     <row r="59" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
@@ -10830,14 +10887,15 @@
       <c r="CV59" s="3"/>
       <c r="CW59" s="3"/>
       <c r="CX59" s="3"/>
-      <c r="CY59" s="26"/>
+      <c r="CY59" s="3"/>
       <c r="CZ59" s="26"/>
       <c r="DA59" s="26"/>
       <c r="DB59" s="26"/>
+      <c r="DC59" s="26"/>
     </row>
     <row r="60" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -10940,10 +10998,11 @@
       <c r="CV60" s="3"/>
       <c r="CW60" s="3"/>
       <c r="CX60" s="3"/>
-      <c r="CY60" s="26"/>
+      <c r="CY60" s="3"/>
       <c r="CZ60" s="26"/>
       <c r="DA60" s="26"/>
       <c r="DB60" s="26"/>
+      <c r="DC60" s="26"/>
     </row>
     <row r="61" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A61" s="3"/>
@@ -11048,10 +11107,11 @@
       <c r="CV61" s="3"/>
       <c r="CW61" s="3"/>
       <c r="CX61" s="3"/>
-      <c r="CY61" s="26"/>
+      <c r="CY61" s="3"/>
       <c r="CZ61" s="26"/>
       <c r="DA61" s="26"/>
       <c r="DB61" s="26"/>
+      <c r="DC61" s="26"/>
     </row>
     <row r="62" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
@@ -11158,14 +11218,15 @@
       <c r="CV62" s="3"/>
       <c r="CW62" s="3"/>
       <c r="CX62" s="3"/>
-      <c r="CY62" s="26"/>
+      <c r="CY62" s="3"/>
       <c r="CZ62" s="26"/>
       <c r="DA62" s="26"/>
       <c r="DB62" s="26"/>
+      <c r="DC62" s="26"/>
     </row>
     <row r="63" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -11268,10 +11329,11 @@
       <c r="CV63" s="3"/>
       <c r="CW63" s="3"/>
       <c r="CX63" s="3"/>
-      <c r="CY63" s="26"/>
+      <c r="CY63" s="3"/>
       <c r="CZ63" s="26"/>
       <c r="DA63" s="26"/>
       <c r="DB63" s="26"/>
+      <c r="DC63" s="26"/>
     </row>
     <row r="64" spans="1:175" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
@@ -11378,10 +11440,11 @@
       <c r="CV64" s="3"/>
       <c r="CW64" s="3"/>
       <c r="CX64" s="3"/>
-      <c r="CY64" s="26"/>
+      <c r="CY64" s="3"/>
       <c r="CZ64" s="26"/>
       <c r="DA64" s="26"/>
       <c r="DB64" s="26"/>
+      <c r="DC64" s="26"/>
     </row>
     <row r="65" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A65" s="3"/>
@@ -11486,10 +11549,11 @@
       <c r="CV65" s="3"/>
       <c r="CW65" s="3"/>
       <c r="CX65" s="3"/>
-      <c r="CY65" s="26"/>
+      <c r="CY65" s="3"/>
       <c r="CZ65" s="26"/>
       <c r="DA65" s="26"/>
       <c r="DB65" s="26"/>
+      <c r="DC65" s="26"/>
     </row>
     <row r="66" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A66" s="13"/>
@@ -11644,12 +11708,13 @@
       <c r="CV66" s="25"/>
       <c r="CW66" s="25"/>
       <c r="CX66" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="CY66" s="27"/>
+        <v>51</v>
+      </c>
+      <c r="CY66" s="25"/>
       <c r="CZ66" s="27"/>
       <c r="DA66" s="27"/>
       <c r="DB66" s="27"/>
+      <c r="DC66" s="27"/>
     </row>
     <row r="67" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
@@ -11958,10 +12023,13 @@
       <c r="CX67" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="CY67" s="28"/>
+      <c r="CY67" s="4" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ67" s="28"/>
       <c r="DA67" s="28"/>
       <c r="DB67" s="28"/>
+      <c r="DC67" s="28"/>
     </row>
     <row r="68" spans="1:179" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="5"/>
@@ -12066,10 +12134,11 @@
       <c r="CV68" s="3"/>
       <c r="CW68" s="3"/>
       <c r="CX68" s="3"/>
-      <c r="CY68" s="26"/>
+      <c r="CY68" s="3"/>
       <c r="CZ68" s="26"/>
       <c r="DA68" s="26"/>
       <c r="DB68" s="26"/>
+      <c r="DC68" s="26"/>
     </row>
     <row r="69" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="24" t="s">
@@ -12376,13 +12445,15 @@
         <v>9.5886170407569011</v>
       </c>
       <c r="CX69" s="12">
-        <v>3.9349019577467033</v>
-      </c>
-      <c r="CY69" s="14"/>
+        <v>2.5962926718435995</v>
+      </c>
+      <c r="CY69" s="12">
+        <v>0.46817010379436397</v>
+      </c>
       <c r="CZ69" s="14"/>
       <c r="DA69" s="14"/>
       <c r="DB69" s="14"/>
-      <c r="DC69" s="20"/>
+      <c r="DC69" s="14"/>
       <c r="DD69" s="20"/>
       <c r="DE69" s="20"/>
       <c r="DF69" s="20"/>
@@ -12757,13 +12828,15 @@
         <v>4.081008142000158</v>
       </c>
       <c r="CX70" s="12">
-        <v>3.884177735188004</v>
-      </c>
-      <c r="CY70" s="14"/>
+        <v>3.3131023121708125</v>
+      </c>
+      <c r="CY70" s="12">
+        <v>2.8189664038445557</v>
+      </c>
       <c r="CZ70" s="14"/>
       <c r="DA70" s="14"/>
       <c r="DB70" s="14"/>
-      <c r="DC70" s="20"/>
+      <c r="DC70" s="14"/>
       <c r="DD70" s="20"/>
       <c r="DE70" s="20"/>
       <c r="DF70" s="20"/>
@@ -12935,11 +13008,11 @@
       <c r="CV71" s="7"/>
       <c r="CW71" s="7"/>
       <c r="CX71" s="7"/>
-      <c r="CY71" s="6"/>
+      <c r="CY71" s="7"/>
       <c r="CZ71" s="6"/>
       <c r="DA71" s="6"/>
       <c r="DB71" s="6"/>
-      <c r="DC71" s="20"/>
+      <c r="DC71" s="6"/>
       <c r="DD71" s="20"/>
       <c r="DE71" s="20"/>
       <c r="DF71" s="20"/>
@@ -13314,13 +13387,15 @@
         <v>7.5833165264184146</v>
       </c>
       <c r="CX72" s="12">
-        <v>3.9130106477429365</v>
-      </c>
-      <c r="CY72" s="14"/>
+        <v>2.9056498439901048</v>
+      </c>
+      <c r="CY72" s="12">
+        <v>1.3615121529479097</v>
+      </c>
       <c r="CZ72" s="14"/>
       <c r="DA72" s="14"/>
       <c r="DB72" s="14"/>
-      <c r="DC72" s="20"/>
+      <c r="DC72" s="14"/>
       <c r="DD72" s="20"/>
       <c r="DE72" s="20"/>
       <c r="DF72" s="20"/>
@@ -13493,10 +13568,11 @@
       <c r="CV73" s="9"/>
       <c r="CW73" s="9"/>
       <c r="CX73" s="9"/>
-      <c r="CY73" s="29"/>
+      <c r="CY73" s="9"/>
       <c r="CZ73" s="29"/>
       <c r="DA73" s="29"/>
       <c r="DB73" s="29"/>
+      <c r="DC73" s="29"/>
     </row>
     <row r="74" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A74" s="10" t="s">
@@ -13603,10 +13679,11 @@
       <c r="CV74" s="3"/>
       <c r="CW74" s="3"/>
       <c r="CX74" s="3"/>
-      <c r="CY74" s="26"/>
+      <c r="CY74" s="3"/>
       <c r="CZ74" s="26"/>
       <c r="DA74" s="26"/>
       <c r="DB74" s="26"/>
+      <c r="DC74" s="26"/>
     </row>
     <row r="75" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="7"/>
@@ -13710,11 +13787,11 @@
       <c r="CV75" s="20"/>
       <c r="CW75" s="20"/>
       <c r="CX75" s="20"/>
-      <c r="CY75" s="19"/>
+      <c r="CY75" s="20"/>
       <c r="CZ75" s="19"/>
       <c r="DA75" s="19"/>
       <c r="DB75" s="19"/>
-      <c r="DC75" s="20"/>
+      <c r="DC75" s="19"/>
       <c r="DD75" s="20"/>
       <c r="DE75" s="20"/>
       <c r="DF75" s="20"/>
@@ -13890,7 +13967,7 @@
       <c r="CZ76" s="6"/>
       <c r="DA76" s="6"/>
       <c r="DB76" s="6"/>
-      <c r="DC76" s="20"/>
+      <c r="DC76" s="6"/>
       <c r="DD76" s="20"/>
       <c r="DE76" s="20"/>
       <c r="DF76" s="20"/>
@@ -14073,10 +14150,11 @@
       <c r="CZ77" s="26"/>
       <c r="DA77" s="26"/>
       <c r="DB77" s="26"/>
+      <c r="DC77" s="26"/>
     </row>
     <row r="78" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -14183,6 +14261,7 @@
       <c r="CZ78" s="26"/>
       <c r="DA78" s="26"/>
       <c r="DB78" s="26"/>
+      <c r="DC78" s="26"/>
     </row>
     <row r="79" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A79" s="3"/>
@@ -14291,6 +14370,7 @@
       <c r="CZ79" s="26"/>
       <c r="DA79" s="26"/>
       <c r="DB79" s="26"/>
+      <c r="DC79" s="26"/>
     </row>
     <row r="80" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
@@ -14401,10 +14481,11 @@
       <c r="CZ80" s="26"/>
       <c r="DA80" s="26"/>
       <c r="DB80" s="26"/>
+      <c r="DC80" s="26"/>
     </row>
     <row r="81" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -14511,6 +14592,7 @@
       <c r="CZ81" s="26"/>
       <c r="DA81" s="26"/>
       <c r="DB81" s="26"/>
+      <c r="DC81" s="26"/>
     </row>
     <row r="82" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
@@ -14621,6 +14703,7 @@
       <c r="CZ82" s="26"/>
       <c r="DA82" s="26"/>
       <c r="DB82" s="26"/>
+      <c r="DC82" s="26"/>
     </row>
     <row r="83" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A83" s="3"/>
@@ -14729,6 +14812,7 @@
       <c r="CZ83" s="3"/>
       <c r="DA83" s="3"/>
       <c r="DB83" s="3"/>
+      <c r="DC83" s="3"/>
     </row>
     <row r="84" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A84" s="13"/>
@@ -14891,6 +14975,7 @@
       <c r="DB84" s="25">
         <v>2026</v>
       </c>
+      <c r="DC84" s="25"/>
     </row>
     <row r="85" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
@@ -15210,6 +15295,9 @@
       </c>
       <c r="DB85" s="11" t="s">
         <v>2</v>
+      </c>
+      <c r="DC85" s="11" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="86" spans="1:179" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -15319,6 +15407,7 @@
       <c r="CZ86" s="3"/>
       <c r="DA86" s="3"/>
       <c r="DB86" s="3"/>
+      <c r="DC86" s="3"/>
     </row>
     <row r="87" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="24" t="s">
@@ -15637,9 +15726,11 @@
         <v>118.03028529977399</v>
       </c>
       <c r="DB87" s="12">
-        <v>119.46591334378152</v>
-      </c>
-      <c r="DC87" s="20"/>
+        <v>119.46591334378154</v>
+      </c>
+      <c r="DC87" s="12">
+        <v>121.6851380873792</v>
+      </c>
       <c r="DD87" s="20"/>
       <c r="DE87" s="20"/>
       <c r="DF87" s="20"/>
@@ -16030,9 +16121,11 @@
         <v>128.59510954066781</v>
       </c>
       <c r="DB88" s="12">
-        <v>132.63885488879382</v>
-      </c>
-      <c r="DC88" s="20"/>
+        <v>132.63586912750722</v>
+      </c>
+      <c r="DC88" s="12">
+        <v>129.03836303779201</v>
+      </c>
       <c r="DD88" s="20"/>
       <c r="DE88" s="20"/>
       <c r="DF88" s="20"/>
@@ -16212,7 +16305,7 @@
       <c r="CZ89" s="7"/>
       <c r="DA89" s="7"/>
       <c r="DB89" s="7"/>
-      <c r="DC89" s="20"/>
+      <c r="DC89" s="7"/>
       <c r="DD89" s="20"/>
       <c r="DE89" s="20"/>
       <c r="DF89" s="20"/>
@@ -16603,9 +16696,11 @@
         <v>121.75167550730966</v>
       </c>
       <c r="DB90" s="12">
-        <v>125.14944908211139</v>
-      </c>
-      <c r="DC90" s="20"/>
+        <v>125.17224292771381</v>
+      </c>
+      <c r="DC90" s="12">
+        <v>124.51966629366009</v>
+      </c>
       <c r="DD90" s="20"/>
       <c r="DE90" s="20"/>
       <c r="DF90" s="20"/>
@@ -16786,6 +16881,7 @@
       <c r="CZ91" s="9"/>
       <c r="DA91" s="9"/>
       <c r="DB91" s="9"/>
+      <c r="DC91" s="9"/>
     </row>
     <row r="92" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A92" s="10" t="s">
@@ -16896,6 +16992,7 @@
       <c r="CZ92" s="3"/>
       <c r="DA92" s="3"/>
       <c r="DB92" s="3"/>
+      <c r="DC92" s="3"/>
     </row>
     <row r="93" spans="1:179" x14ac:dyDescent="0.25">
       <c r="B93" s="3"/>
@@ -17003,6 +17100,7 @@
       <c r="CZ93" s="3"/>
       <c r="DA93" s="3"/>
       <c r="DB93" s="3"/>
+      <c r="DC93" s="3"/>
     </row>
     <row r="94" spans="1:179" x14ac:dyDescent="0.25">
       <c r="B94" s="3"/>
@@ -17110,6 +17208,7 @@
       <c r="CZ94" s="3"/>
       <c r="DA94" s="3"/>
       <c r="DB94" s="3"/>
+      <c r="DC94" s="3"/>
     </row>
     <row r="95" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
@@ -17220,6 +17319,7 @@
       <c r="CZ95" s="3"/>
       <c r="DA95" s="3"/>
       <c r="DB95" s="3"/>
+      <c r="DC95" s="3"/>
     </row>
     <row r="96" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
@@ -17330,10 +17430,11 @@
       <c r="CZ96" s="3"/>
       <c r="DA96" s="3"/>
       <c r="DB96" s="3"/>
+      <c r="DC96" s="3"/>
     </row>
     <row r="97" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -17440,6 +17541,7 @@
       <c r="CZ97" s="3"/>
       <c r="DA97" s="3"/>
       <c r="DB97" s="3"/>
+      <c r="DC97" s="3"/>
     </row>
     <row r="98" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A98" s="3"/>
@@ -17548,6 +17650,7 @@
       <c r="CZ98" s="3"/>
       <c r="DA98" s="3"/>
       <c r="DB98" s="3"/>
+      <c r="DC98" s="3"/>
     </row>
     <row r="99" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
@@ -17658,10 +17761,11 @@
       <c r="CZ99" s="3"/>
       <c r="DA99" s="3"/>
       <c r="DB99" s="3"/>
+      <c r="DC99" s="3"/>
     </row>
     <row r="100" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -17768,6 +17872,7 @@
       <c r="CZ100" s="3"/>
       <c r="DA100" s="3"/>
       <c r="DB100" s="3"/>
+      <c r="DC100" s="3"/>
     </row>
     <row r="101" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
@@ -17878,6 +17983,7 @@
       <c r="CZ101" s="3"/>
       <c r="DA101" s="3"/>
       <c r="DB101" s="3"/>
+      <c r="DC101" s="3"/>
     </row>
     <row r="102" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A102" s="3"/>
@@ -17986,6 +18092,7 @@
       <c r="CZ102" s="3"/>
       <c r="DA102" s="3"/>
       <c r="DB102" s="3"/>
+      <c r="DC102" s="3"/>
     </row>
     <row r="103" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A103" s="13"/>
@@ -18148,6 +18255,7 @@
       <c r="DB103" s="25">
         <v>2026</v>
       </c>
+      <c r="DC103" s="25"/>
     </row>
     <row r="104" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
@@ -18467,6 +18575,9 @@
       </c>
       <c r="DB104" s="11" t="s">
         <v>2</v>
+      </c>
+      <c r="DC104" s="11" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:179" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -18576,6 +18687,7 @@
       <c r="CZ105" s="3"/>
       <c r="DA105" s="3"/>
       <c r="DB105" s="3"/>
+      <c r="DC105" s="3"/>
     </row>
     <row r="106" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="24" t="s">
@@ -18894,9 +19006,11 @@
         <v>62.795759746145841</v>
       </c>
       <c r="DB106" s="12">
-        <v>54.272479592168423</v>
-      </c>
-      <c r="DC106" s="20"/>
+        <v>54.088076488122198</v>
+      </c>
+      <c r="DC106" s="12">
+        <v>60.053031441836637</v>
+      </c>
       <c r="DD106" s="20"/>
       <c r="DE106" s="20"/>
       <c r="DF106" s="20"/>
@@ -19287,9 +19401,11 @@
         <v>37.204240253854152</v>
       </c>
       <c r="DB107" s="12">
-        <v>45.727520407831577</v>
-      </c>
-      <c r="DC107" s="20"/>
+        <v>45.911923511877795</v>
+      </c>
+      <c r="DC107" s="12">
+        <v>39.94696855816337</v>
+      </c>
       <c r="DD107" s="20"/>
       <c r="DE107" s="20"/>
       <c r="DF107" s="20"/>
@@ -19469,7 +19585,7 @@
       <c r="CZ108" s="7"/>
       <c r="DA108" s="7"/>
       <c r="DB108" s="7"/>
-      <c r="DC108" s="20"/>
+      <c r="DC108" s="7"/>
       <c r="DD108" s="20"/>
       <c r="DE108" s="20"/>
       <c r="DF108" s="20"/>
@@ -19862,7 +19978,9 @@
       <c r="DB109" s="12">
         <v>100</v>
       </c>
-      <c r="DC109" s="20"/>
+      <c r="DC109" s="12">
+        <v>100</v>
+      </c>
       <c r="DD109" s="20"/>
       <c r="DE109" s="20"/>
       <c r="DF109" s="20"/>
@@ -20043,6 +20161,7 @@
       <c r="CZ110" s="9"/>
       <c r="DA110" s="9"/>
       <c r="DB110" s="9"/>
+      <c r="DC110" s="9"/>
     </row>
     <row r="111" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A111" s="10" t="s">
@@ -20153,6 +20272,7 @@
       <c r="CZ111" s="3"/>
       <c r="DA111" s="3"/>
       <c r="DB111" s="3"/>
+      <c r="DC111" s="3"/>
     </row>
     <row r="112" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="7"/>
@@ -20260,7 +20380,7 @@
       <c r="CZ112" s="7"/>
       <c r="DA112" s="7"/>
       <c r="DB112" s="7"/>
-      <c r="DC112" s="20"/>
+      <c r="DC112" s="7"/>
       <c r="DD112" s="20"/>
       <c r="DE112" s="20"/>
       <c r="DF112" s="20"/>
@@ -20440,7 +20560,7 @@
       <c r="CZ113" s="7"/>
       <c r="DA113" s="7"/>
       <c r="DB113" s="7"/>
-      <c r="DC113" s="20"/>
+      <c r="DC113" s="7"/>
       <c r="DD113" s="20"/>
       <c r="DE113" s="20"/>
       <c r="DF113" s="20"/>
@@ -20623,6 +20743,7 @@
       <c r="CZ114" s="3"/>
       <c r="DA114" s="3"/>
       <c r="DB114" s="3"/>
+      <c r="DC114" s="3"/>
     </row>
     <row r="115" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
@@ -20733,10 +20854,11 @@
       <c r="CZ115" s="3"/>
       <c r="DA115" s="3"/>
       <c r="DB115" s="3"/>
+      <c r="DC115" s="3"/>
     </row>
     <row r="116" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -20843,6 +20965,7 @@
       <c r="CZ116" s="3"/>
       <c r="DA116" s="3"/>
       <c r="DB116" s="3"/>
+      <c r="DC116" s="3"/>
     </row>
     <row r="117" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A117" s="3"/>
@@ -20951,6 +21074,7 @@
       <c r="CZ117" s="3"/>
       <c r="DA117" s="3"/>
       <c r="DB117" s="3"/>
+      <c r="DC117" s="3"/>
     </row>
     <row r="118" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
@@ -21061,10 +21185,11 @@
       <c r="CZ118" s="3"/>
       <c r="DA118" s="3"/>
       <c r="DB118" s="3"/>
+      <c r="DC118" s="3"/>
     </row>
     <row r="119" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -21171,6 +21296,7 @@
       <c r="CZ119" s="3"/>
       <c r="DA119" s="3"/>
       <c r="DB119" s="3"/>
+      <c r="DC119" s="3"/>
     </row>
     <row r="120" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
@@ -21281,6 +21407,7 @@
       <c r="CZ120" s="3"/>
       <c r="DA120" s="3"/>
       <c r="DB120" s="3"/>
+      <c r="DC120" s="3"/>
     </row>
     <row r="121" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A121" s="3"/>
@@ -21389,6 +21516,7 @@
       <c r="CZ121" s="3"/>
       <c r="DA121" s="3"/>
       <c r="DB121" s="3"/>
+      <c r="DC121" s="3"/>
     </row>
     <row r="122" spans="1:179" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A122" s="13"/>
@@ -21551,6 +21679,7 @@
       <c r="DB122" s="25">
         <v>2026</v>
       </c>
+      <c r="DC122" s="25"/>
     </row>
     <row r="123" spans="1:179" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A123" s="4" t="s">
@@ -21870,6 +21999,9 @@
       </c>
       <c r="DB123" s="11" t="s">
         <v>2</v>
+      </c>
+      <c r="DC123" s="11" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="124" spans="1:179" s="17" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -21979,6 +22111,7 @@
       <c r="CZ124" s="3"/>
       <c r="DA124" s="3"/>
       <c r="DB124" s="3"/>
+      <c r="DC124" s="3"/>
     </row>
     <row r="125" spans="1:179" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="24" t="s">
@@ -22297,9 +22430,11 @@
         <v>64.775654353708205</v>
       </c>
       <c r="DB125" s="12">
-        <v>56.854467782240903</v>
-      </c>
-      <c r="DC125" s="20"/>
+        <v>56.671611677059239</v>
+      </c>
+      <c r="DC125" s="12">
+        <v>61.451904091118813</v>
+      </c>
       <c r="DD125" s="20"/>
       <c r="DE125" s="20"/>
       <c r="DF125" s="20"/>
@@ -22690,9 +22825,11 @@
         <v>35.224345646291802</v>
       </c>
       <c r="DB126" s="12">
-        <v>43.14553221775909</v>
-      </c>
-      <c r="DC126" s="20"/>
+        <v>43.328388322940761</v>
+      </c>
+      <c r="DC126" s="12">
+        <v>38.548095908881187</v>
+      </c>
       <c r="DD126" s="20"/>
       <c r="DE126" s="20"/>
       <c r="DF126" s="20"/>
@@ -22872,7 +23009,7 @@
       <c r="CZ127" s="7"/>
       <c r="DA127" s="7"/>
       <c r="DB127" s="7"/>
-      <c r="DC127" s="20"/>
+      <c r="DC127" s="7"/>
       <c r="DD127" s="20"/>
       <c r="DE127" s="20"/>
       <c r="DF127" s="20"/>
@@ -23265,7 +23402,9 @@
       <c r="DB128" s="12">
         <v>100</v>
       </c>
-      <c r="DC128" s="20"/>
+      <c r="DC128" s="12">
+        <v>100</v>
+      </c>
       <c r="DD128" s="20"/>
       <c r="DE128" s="20"/>
       <c r="DF128" s="20"/>
@@ -23339,7 +23478,7 @@
       <c r="FV128" s="20"/>
       <c r="FW128" s="20"/>
     </row>
-    <row r="129" spans="1:106" s="17" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:107" s="17" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="9"/>
       <c r="B129" s="9"/>
       <c r="C129" s="9"/>
@@ -23446,8 +23585,9 @@
       <c r="CZ129" s="9"/>
       <c r="DA129" s="9"/>
       <c r="DB129" s="9"/>
+      <c r="DC129" s="9"/>
     </row>
-    <row r="130" spans="1:106" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:107" s="17" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A130" s="10" t="s">
         <v>6</v>
       </c>
@@ -23556,25 +23696,28 @@
       <c r="CZ130" s="3"/>
       <c r="DA130" s="3"/>
       <c r="DB130" s="3"/>
+      <c r="DC130" s="3"/>
     </row>
-    <row r="131" spans="1:106" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:107" x14ac:dyDescent="0.25">
       <c r="CX131" s="22"/>
       <c r="CY131" s="22"/>
       <c r="CZ131" s="22"/>
       <c r="DA131" s="22"/>
       <c r="DB131" s="22"/>
+      <c r="DC131" s="22"/>
     </row>
-    <row r="132" spans="1:106" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:107" x14ac:dyDescent="0.25">
       <c r="CT132" s="23"/>
       <c r="CU132" s="23"/>
       <c r="CV132" s="23"/>
-      <c r="CX132" s="23"/>
-      <c r="CY132" s="23"/>
-      <c r="CZ132" s="23"/>
-      <c r="DA132" s="23"/>
-      <c r="DB132" s="23"/>
+      <c r="CX132" s="22"/>
+      <c r="CY132" s="22"/>
+      <c r="CZ132" s="22"/>
+      <c r="DA132" s="22"/>
+      <c r="DB132" s="22"/>
+      <c r="DC132" s="22"/>
     </row>
-    <row r="133" spans="1:106" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:107" x14ac:dyDescent="0.25">
       <c r="CT133" s="23"/>
       <c r="CU133" s="23"/>
       <c r="CV133" s="23"/>
@@ -23583,8 +23726,9 @@
       <c r="CZ133" s="23"/>
       <c r="DA133" s="23"/>
       <c r="DB133" s="23"/>
+      <c r="DC133" s="23"/>
     </row>
-    <row r="134" spans="1:106" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:107" x14ac:dyDescent="0.25">
       <c r="CT134" s="23"/>
       <c r="CU134" s="23"/>
       <c r="CV134" s="23"/>
@@ -23593,8 +23737,9 @@
       <c r="CZ134" s="23"/>
       <c r="DA134" s="23"/>
       <c r="DB134" s="23"/>
+      <c r="DC134" s="23"/>
     </row>
-    <row r="135" spans="1:106" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:107" x14ac:dyDescent="0.25">
       <c r="CT135" s="23"/>
       <c r="CU135" s="23"/>
       <c r="CV135" s="23"/>
@@ -23603,8 +23748,9 @@
       <c r="CZ135" s="23"/>
       <c r="DA135" s="23"/>
       <c r="DB135" s="23"/>
+      <c r="DC135" s="23"/>
     </row>
-    <row r="136" spans="1:106" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:107" x14ac:dyDescent="0.25">
       <c r="CT136" s="23"/>
       <c r="CU136" s="23"/>
       <c r="CV136" s="23"/>
@@ -23613,6 +23759,15 @@
       <c r="CZ136" s="23"/>
       <c r="DA136" s="23"/>
       <c r="DB136" s="23"/>
+      <c r="DC136" s="23"/>
+    </row>
+    <row r="137" spans="1:107" x14ac:dyDescent="0.25">
+      <c r="CX137" s="23"/>
+      <c r="CY137" s="23"/>
+      <c r="CZ137" s="23"/>
+      <c r="DA137" s="23"/>
+      <c r="DB137" s="23"/>
+      <c r="DC137" s="23"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
@@ -23620,9 +23775,9 @@
   <pageSetup paperSize="9" scale="47" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="38" max="105" man="1"/>
-    <brk id="76" max="105" man="1"/>
-    <brk id="94" max="105" man="1"/>
+    <brk id="38" max="106" man="1"/>
+    <brk id="76" max="106" man="1"/>
+    <brk id="94" max="106" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>